--- a/04_Network/05_classify_and_associate_modules/c_data/05_classify_and_associate_modules.xlsx
+++ b/04_Network/05_classify_and_associate_modules/c_data/05_classify_and_associate_modules.xlsx
@@ -49,7 +49,7 @@
     <t>module_by_arm</t>
   </si>
   <si>
-    <t>Every within-arm correlation, per arm, window, outcome and module.</t>
+    <t>Every within-arm correlation with exact p, per arm, window, outcome and module.</t>
   </si>
   <si>
     <t>input_manifest</t>
@@ -13060,7 +13060,7 @@
         <v>-0.6</v>
       </c>
       <c r="G2">
-        <v>0.2079999999999997</v>
+        <v>0.2416666666666667</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -13083,7 +13083,7 @@
         <v>-0.8285714285714285</v>
       </c>
       <c r="G3">
-        <v>0.04156268221574345</v>
+        <v>0.05833333333333333</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -13106,7 +13106,7 @@
         <v>0.6571428571428571</v>
       </c>
       <c r="G4">
-        <v>0.1561749271137025</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -13129,7 +13129,7 @@
         <v>-0.9428571428571428</v>
       </c>
       <c r="G5">
-        <v>0.004804664723032068</v>
+        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -13152,7 +13152,7 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="G6">
-        <v>0.7871720116618075</v>
+        <v>0.8027777777777778</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -13175,7 +13175,7 @@
         <v>-0.8857142857142858</v>
       </c>
       <c r="G7">
-        <v>0.01884548104956268</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -13198,7 +13198,7 @@
         <v>-0.5428571428571428</v>
       </c>
       <c r="G8">
-        <v>0.2657026239067054</v>
+        <v>0.2972222222222222</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -13221,7 +13221,7 @@
         <v>0.3714285714285714</v>
       </c>
       <c r="G9">
-        <v>0.4684781341107874</v>
+        <v>0.4972222222222222</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -13244,7 +13244,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="G10">
-        <v>0.1107871720116618</v>
+        <v>0.1361111111111111</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -13267,7 +13267,7 @@
         <v>0.7714285714285715</v>
       </c>
       <c r="G11">
-        <v>0.07239650145772589</v>
+        <v>0.1027777777777778</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -13290,7 +13290,7 @@
         <v>0.8857142857142858</v>
       </c>
       <c r="G12">
-        <v>0.01884548104956266</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -13313,7 +13313,7 @@
         <v>0.5428571428571428</v>
       </c>
       <c r="G13">
-        <v>0.2657026239067054</v>
+        <v>0.2972222222222222</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -13336,7 +13336,7 @@
         <v>-0.2571428571428572</v>
       </c>
       <c r="G14">
-        <v>0.6227871720116618</v>
+        <v>0.6583333333333333</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -13359,7 +13359,7 @@
         <v>-0.3714285714285714</v>
       </c>
       <c r="G15">
-        <v>0.4684781341107874</v>
+        <v>0.4972222222222222</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -13382,7 +13382,7 @@
         <v>0.2</v>
       </c>
       <c r="G16">
-        <v>0.7040000000000001</v>
+        <v>0.7138888888888889</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -13405,7 +13405,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="G17">
-        <v>0.7871720116618076</v>
+        <v>0.8027777777777778</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -13428,7 +13428,7 @@
         <v>0.4857142857142857</v>
       </c>
       <c r="G18">
-        <v>0.3287230320699709</v>
+        <v>0.3555555555555556</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -13451,7 +13451,7 @@
         <v>-0.5428571428571428</v>
       </c>
       <c r="G19">
-        <v>0.2657026239067054</v>
+        <v>0.2972222222222222</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -13474,7 +13474,7 @@
         <v>0.2571428571428572</v>
       </c>
       <c r="G20">
-        <v>0.6227871720116618</v>
+        <v>0.6583333333333333</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -13497,7 +13497,7 @@
         <v>0.02857142857142857</v>
       </c>
       <c r="G21">
-        <v>0.9571545189504373</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -13520,7 +13520,7 @@
         <v>-0.3142857142857143</v>
       </c>
       <c r="G22">
-        <v>0.5440932944606414</v>
+        <v>0.5638888888888889</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -13543,7 +13543,7 @@
         <v>-0.2</v>
       </c>
       <c r="G23">
-        <v>0.7040000000000001</v>
+        <v>0.7138888888888889</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -13566,7 +13566,7 @@
         <v>0.2571428571428572</v>
       </c>
       <c r="G24">
-        <v>0.6227871720116618</v>
+        <v>0.6583333333333333</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -13589,7 +13589,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="G25">
-        <v>0.3965014577259475</v>
+        <v>0.4194444444444445</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -13612,7 +13612,7 @@
         <v>-0.2571428571428572</v>
       </c>
       <c r="G26">
-        <v>0.6227871720116618</v>
+        <v>0.6583333333333333</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -13635,7 +13635,7 @@
         <v>-0.6</v>
       </c>
       <c r="G27">
-        <v>0.2079999999999997</v>
+        <v>0.2416666666666667</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -13658,7 +13658,7 @@
         <v>0.7714285714285715</v>
       </c>
       <c r="G28">
-        <v>0.07239650145772589</v>
+        <v>0.1027777777777778</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -13681,7 +13681,7 @@
         <v>-0.4857142857142857</v>
       </c>
       <c r="G29">
-        <v>0.3287230320699709</v>
+        <v>0.3555555555555556</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -13704,7 +13704,7 @@
         <v>0.02857142857142857</v>
       </c>
       <c r="G30">
-        <v>0.9571545189504373</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -13727,7 +13727,7 @@
         <v>-0.6571428571428571</v>
       </c>
       <c r="G31">
-        <v>0.1561749271137025</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -13750,7 +13750,7 @@
         <v>-0.5428571428571428</v>
       </c>
       <c r="G32">
-        <v>0.2657026239067054</v>
+        <v>0.2972222222222222</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -13773,7 +13773,7 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="G33">
-        <v>0.7871720116618075</v>
+        <v>0.8027777777777778</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -13796,7 +13796,7 @@
         <v>-0.7714285714285715</v>
       </c>
       <c r="G34">
-        <v>0.07239650145772594</v>
+        <v>0.1027777777777778</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -13819,7 +13819,7 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="G35">
-        <v>0.7871720116618075</v>
+        <v>0.8027777777777778</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -13842,7 +13842,7 @@
         <v>0.3714285714285714</v>
       </c>
       <c r="G36">
-        <v>0.4684781341107874</v>
+        <v>0.4972222222222222</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -13865,7 +13865,7 @@
         <v>0.8857142857142858</v>
       </c>
       <c r="G37">
-        <v>0.01884548104956266</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -13888,7 +13888,7 @@
         <v>-0.4857142857142857</v>
       </c>
       <c r="G38">
-        <v>0.3287230320699709</v>
+        <v>0.3555555555555556</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -13911,7 +13911,7 @@
         <v>-0.6</v>
       </c>
       <c r="G39">
-        <v>0.2079999999999997</v>
+        <v>0.2416666666666667</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -13934,7 +13934,7 @@
         <v>0.3714285714285714</v>
       </c>
       <c r="G40">
-        <v>0.4684781341107874</v>
+        <v>0.4972222222222222</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -13957,7 +13957,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="G41">
-        <v>0.3965014577259475</v>
+        <v>0.4194444444444445</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -13980,7 +13980,7 @@
         <v>0.5428571428571428</v>
       </c>
       <c r="G42">
-        <v>0.2657026239067054</v>
+        <v>0.2972222222222222</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -14003,7 +14003,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="G43">
-        <v>0.1107871720116618</v>
+        <v>0.1361111111111111</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -14026,7 +14026,7 @@
         <v>0.02857142857142857</v>
       </c>
       <c r="G44">
-        <v>0.9571545189504373</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -14049,7 +14049,7 @@
         <v>0.2571428571428572</v>
       </c>
       <c r="G45">
-        <v>0.6227871720116618</v>
+        <v>0.6583333333333333</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -14072,7 +14072,7 @@
         <v>-0.6</v>
       </c>
       <c r="G46">
-        <v>0.2079999999999997</v>
+        <v>0.2416666666666667</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -14095,7 +14095,7 @@
         <v>0.08571428571428572</v>
       </c>
       <c r="G47">
-        <v>0.871743440233236</v>
+        <v>0.9194444444444444</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -14118,7 +14118,7 @@
         <v>0.4857142857142857</v>
       </c>
       <c r="G48">
-        <v>0.3287230320699709</v>
+        <v>0.3555555555555556</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -14141,7 +14141,7 @@
         <v>0.5428571428571428</v>
       </c>
       <c r="G49">
-        <v>0.2657026239067054</v>
+        <v>0.2972222222222222</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -14164,7 +14164,7 @@
         <v>0.7142857142857143</v>
       </c>
       <c r="G50">
-        <v>0.1107871720116617</v>
+        <v>0.1361111111111111</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -14187,7 +14187,7 @@
         <v>0.5428571428571428</v>
       </c>
       <c r="G51">
-        <v>0.2657026239067054</v>
+        <v>0.2972222222222222</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -14210,7 +14210,7 @@
         <v>0.08571428571428572</v>
       </c>
       <c r="G52">
-        <v>0.871743440233236</v>
+        <v>0.9194444444444444</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -14233,7 +14233,7 @@
         <v>0.6571428571428571</v>
       </c>
       <c r="G53">
-        <v>0.1561749271137025</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -14256,7 +14256,7 @@
         <v>-0.6</v>
       </c>
       <c r="G54">
-        <v>0.2079999999999997</v>
+        <v>0.2416666666666667</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -14279,7 +14279,7 @@
         <v>0.4857142857142857</v>
       </c>
       <c r="G55">
-        <v>0.3287230320699709</v>
+        <v>0.3555555555555556</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -14302,7 +14302,7 @@
         <v>-0.08571428571428572</v>
       </c>
       <c r="G56">
-        <v>0.8717434402332366</v>
+        <v>0.9194444444444444</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -14325,7 +14325,7 @@
         <v>-0.5428571428571428</v>
       </c>
       <c r="G57">
-        <v>0.2657026239067054</v>
+        <v>0.2972222222222222</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -14348,7 +14348,7 @@
         <v>0.3142857142857143</v>
       </c>
       <c r="G58">
-        <v>0.5440932944606414</v>
+        <v>0.5638888888888889</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -14371,7 +14371,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="G59">
-        <v>0.1107871720116618</v>
+        <v>0.1361111111111111</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -14394,7 +14394,7 @@
         <v>-0.7714285714285715</v>
       </c>
       <c r="G60">
-        <v>0.07239650145772594</v>
+        <v>0.1027777777777778</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -14417,7 +14417,7 @@
         <v>0.2571428571428572</v>
       </c>
       <c r="G61">
-        <v>0.6227871720116618</v>
+        <v>0.6583333333333333</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -14440,7 +14440,7 @@
         <v>0.6957252427829381</v>
       </c>
       <c r="G62">
-        <v>0.124789337440287</v>
+        <v>0.1444444444444444</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -14463,7 +14463,7 @@
         <v>0.6377481392176934</v>
       </c>
       <c r="G63">
-        <v>0.1730711102412597</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -14486,7 +14486,7 @@
         <v>-0.02898855178262242</v>
       </c>
       <c r="G64">
-        <v>0.9565293523898404</v>
+        <v>0.9833333333333333</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -14509,7 +14509,7 @@
         <v>0.7247137945655605</v>
       </c>
       <c r="G65">
-        <v>0.1032428046237077</v>
+        <v>0.1222222222222222</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -14532,7 +14532,7 @@
         <v>-0.550782483869826</v>
       </c>
       <c r="G66">
-        <v>0.2573693316225747</v>
+        <v>0.2722222222222222</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -14555,7 +14555,7 @@
         <v>0.550782483869826</v>
       </c>
       <c r="G67">
-        <v>0.2573693316225745</v>
+        <v>0.2722222222222222</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -14578,7 +14578,7 @@
         <v>0.05797710356524485</v>
       </c>
       <c r="G68">
-        <v>0.9131317851623265</v>
+        <v>0.9333333333333333</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -14601,7 +14601,7 @@
         <v>-0.5217939320872036</v>
       </c>
       <c r="G69">
-        <v>0.2883432338003937</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -14624,7 +14624,7 @@
         <v>0.4058397249567139</v>
       </c>
       <c r="G70">
-        <v>0.4246625075613645</v>
+        <v>0.4333333333333333</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -14647,7 +14647,7 @@
         <v>-0.753702346348183</v>
       </c>
       <c r="G71">
-        <v>0.08352328137325972</v>
+        <v>0.1055555555555556</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -14670,7 +14670,7 @@
         <v>-0.8406680016960502</v>
       </c>
       <c r="G72">
-        <v>0.03605757284515933</v>
+        <v>0.04444444444444445</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -14693,7 +14693,7 @@
         <v>0.1739313106957345</v>
       </c>
       <c r="G73">
-        <v>0.7417339277316277</v>
+        <v>0.7333333333333333</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -14716,7 +14716,7 @@
         <v>0.08571428571428572</v>
       </c>
       <c r="G74">
-        <v>0.871743440233236</v>
+        <v>0.9194444444444444</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -14739,7 +14739,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="G75">
-        <v>0.7871720116618076</v>
+        <v>0.8027777777777778</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -14762,7 +14762,7 @@
         <v>0.4857142857142857</v>
       </c>
       <c r="G76">
-        <v>0.3287230320699709</v>
+        <v>0.3555555555555556</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -14785,7 +14785,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="G77">
-        <v>0.3965014577259475</v>
+        <v>0.4194444444444445</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -14808,7 +14808,7 @@
         <v>-0.6571428571428571</v>
       </c>
       <c r="G78">
-        <v>0.1561749271137025</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -14831,7 +14831,7 @@
         <v>-0.2571428571428572</v>
       </c>
       <c r="G79">
-        <v>0.6227871720116618</v>
+        <v>0.6583333333333333</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -14854,7 +14854,7 @@
         <v>-0.6</v>
       </c>
       <c r="G80">
-        <v>0.2079999999999997</v>
+        <v>0.2416666666666667</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -14877,7 +14877,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="G81">
-        <v>0.7871720116618076</v>
+        <v>0.8027777777777778</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -14900,7 +14900,7 @@
         <v>-0.02857142857142857</v>
       </c>
       <c r="G82">
-        <v>0.9571545189504375</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -14923,7 +14923,7 @@
         <v>0.4857142857142857</v>
       </c>
       <c r="G83">
-        <v>0.3287230320699709</v>
+        <v>0.3555555555555556</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -14946,7 +14946,7 @@
         <v>0.2571428571428572</v>
       </c>
       <c r="G84">
-        <v>0.6227871720116618</v>
+        <v>0.6583333333333333</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -14969,7 +14969,7 @@
         <v>0.3142857142857143</v>
       </c>
       <c r="G85">
-        <v>0.5440932944606414</v>
+        <v>0.5638888888888889</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -14992,7 +14992,7 @@
         <v>0.4857142857142857</v>
       </c>
       <c r="G86">
-        <v>0.3287230320699709</v>
+        <v>0.3555555555555556</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -15015,7 +15015,7 @@
         <v>-0.08571428571428572</v>
       </c>
       <c r="G87">
-        <v>0.8717434402332366</v>
+        <v>0.9194444444444444</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -15038,7 +15038,7 @@
         <v>0.4857142857142857</v>
       </c>
       <c r="G88">
-        <v>0.3287230320699709</v>
+        <v>0.3555555555555556</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -15061,7 +15061,7 @@
         <v>0.2571428571428572</v>
       </c>
       <c r="G89">
-        <v>0.6227871720116618</v>
+        <v>0.6583333333333333</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -15084,7 +15084,7 @@
         <v>-0.2571428571428572</v>
       </c>
       <c r="G90">
-        <v>0.6227871720116618</v>
+        <v>0.6583333333333333</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -15107,7 +15107,7 @@
         <v>-0.2571428571428572</v>
       </c>
       <c r="G91">
-        <v>0.6227871720116618</v>
+        <v>0.6583333333333333</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -15130,7 +15130,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="G92">
-        <v>0.7871720116618076</v>
+        <v>0.8027777777777778</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -15153,7 +15153,7 @@
         <v>-0.6</v>
       </c>
       <c r="G93">
-        <v>0.2079999999999997</v>
+        <v>0.2416666666666667</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -15176,7 +15176,7 @@
         <v>-0.08571428571428572</v>
       </c>
       <c r="G94">
-        <v>0.8717434402332366</v>
+        <v>0.9194444444444444</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -15199,7 +15199,7 @@
         <v>-0.6571428571428571</v>
       </c>
       <c r="G95">
-        <v>0.1561749271137025</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -15222,7 +15222,7 @@
         <v>-0.2</v>
       </c>
       <c r="G96">
-        <v>0.7040000000000001</v>
+        <v>0.7138888888888889</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -15245,7 +15245,7 @@
         <v>0.7142857142857143</v>
       </c>
       <c r="G97">
-        <v>0.1107871720116617</v>
+        <v>0.1361111111111111</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -15268,7 +15268,7 @@
         <v>-0.09999999999999998</v>
       </c>
       <c r="G98">
-        <v>0.8728885715695381</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -15291,7 +15291,7 @@
         <v>-0.5999999999999999</v>
       </c>
       <c r="G99">
-        <v>0.2847569798652939</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -15314,7 +15314,7 @@
         <v>0.5999999999999999</v>
       </c>
       <c r="G100">
-        <v>0.2847569798652939</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -15337,7 +15337,7 @@
         <v>-0.7999999999999998</v>
       </c>
       <c r="G101">
-        <v>0.1040880386618281</v>
+        <v>0.1333333333333333</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -15360,7 +15360,7 @@
         <v>-0.4999999999999999</v>
       </c>
       <c r="G102">
-        <v>0.3910022189557705</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -15383,7 +15383,7 @@
         <v>-0.6999999999999998</v>
       </c>
       <c r="G103">
-        <v>0.1881204043741875</v>
+        <v>0.2333333333333333</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -15406,7 +15406,7 @@
         <v>-0.4999999999999999</v>
       </c>
       <c r="G104">
-        <v>0.3910022189557705</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -15429,7 +15429,7 @@
         <v>0.09999999999999998</v>
       </c>
       <c r="G105">
-        <v>0.8728885715695383</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -15452,7 +15452,7 @@
         <v>-0.2</v>
       </c>
       <c r="G106">
-        <v>0.7470600781046621</v>
+        <v>0.7833333333333333</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -15475,7 +15475,7 @@
         <v>0.5999999999999999</v>
       </c>
       <c r="G107">
-        <v>0.2847569798652939</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -15498,7 +15498,7 @@
         <v>0.7999999999999998</v>
       </c>
       <c r="G108">
-        <v>0.104088038661828</v>
+        <v>0.1333333333333333</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -15521,7 +15521,7 @@
         <v>0.2999999999999999</v>
       </c>
       <c r="G109">
-        <v>0.6238376647810731</v>
+        <v>0.6833333333333333</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -15544,7 +15544,7 @@
         <v>-0.3714285714285714</v>
       </c>
       <c r="G110">
-        <v>0.4684781341107874</v>
+        <v>0.4972222222222222</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -15567,7 +15567,7 @@
         <v>-0.5428571428571428</v>
       </c>
       <c r="G111">
-        <v>0.2657026239067054</v>
+        <v>0.2972222222222222</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -15590,7 +15590,7 @@
         <v>0.6</v>
       </c>
       <c r="G112">
-        <v>0.2079999999999998</v>
+        <v>0.2416666666666667</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -15613,7 +15613,7 @@
         <v>-0.5428571428571428</v>
       </c>
       <c r="G113">
-        <v>0.2657026239067054</v>
+        <v>0.2972222222222222</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -15636,7 +15636,7 @@
         <v>0.02857142857142857</v>
       </c>
       <c r="G114">
-        <v>0.9571545189504373</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -15659,7 +15659,7 @@
         <v>-0.3714285714285714</v>
       </c>
       <c r="G115">
-        <v>0.4684781341107874</v>
+        <v>0.4972222222222222</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -15682,7 +15682,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="G116">
-        <v>0.1107871720116618</v>
+        <v>0.1361111111111111</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -15705,7 +15705,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="G117">
-        <v>0.3965014577259475</v>
+        <v>0.4194444444444445</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -15728,7 +15728,7 @@
         <v>-0.8285714285714285</v>
       </c>
       <c r="G118">
-        <v>0.04156268221574345</v>
+        <v>0.05833333333333333</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -15751,7 +15751,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="G119">
-        <v>0.3965014577259475</v>
+        <v>0.4194444444444445</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -15774,7 +15774,7 @@
         <v>0.3714285714285714</v>
       </c>
       <c r="G120">
-        <v>0.4684781341107874</v>
+        <v>0.4972222222222222</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -15797,7 +15797,7 @@
         <v>0.5428571428571428</v>
       </c>
       <c r="G121">
-        <v>0.2657026239067054</v>
+        <v>0.2972222222222222</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -15820,7 +15820,7 @@
         <v>0.5714285714285713</v>
       </c>
       <c r="G122">
-        <v>0.1802019889115277</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -15843,7 +15843,7 @@
         <v>0.6428571428571427</v>
       </c>
       <c r="G123">
-        <v>0.1193923734274112</v>
+        <v>0.1388888888888889</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -15866,7 +15866,7 @@
         <v>-0.2857142857142856</v>
       </c>
       <c r="G124">
-        <v>0.5345092286010411</v>
+        <v>0.555952380952381</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -15889,7 +15889,7 @@
         <v>0.607142857142857</v>
       </c>
       <c r="G125">
-        <v>0.1482311614811615</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -15912,7 +15912,7 @@
         <v>-0.1071428571428571</v>
       </c>
       <c r="G126">
-        <v>0.8191508555699912</v>
+        <v>0.8396825396825397</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -15935,7 +15935,7 @@
         <v>0.8214285714285713</v>
       </c>
       <c r="G127">
-        <v>0.02344880834569154</v>
+        <v>0.03412698412698412</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -15958,7 +15958,7 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="G128">
-        <v>0.7599453002180929</v>
+        <v>0.7825396825396825</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -15981,7 +15981,7 @@
         <v>-0.2857142857142856</v>
       </c>
       <c r="G129">
-        <v>0.5345092286010411</v>
+        <v>0.555952380952381</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -16004,7 +16004,7 @@
         <v>0.2857142857142856</v>
       </c>
       <c r="G130">
-        <v>0.5345092286010409</v>
+        <v>0.555952380952381</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -16027,7 +16027,7 @@
         <v>-0.2857142857142856</v>
       </c>
       <c r="G131">
-        <v>0.5345092286010411</v>
+        <v>0.555952380952381</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -16050,7 +16050,7 @@
         <v>-0.7499999999999998</v>
       </c>
       <c r="G132">
-        <v>0.05218140045705796</v>
+        <v>0.06626984126984127</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -16073,7 +16073,7 @@
         <v>-0.4999999999999999</v>
       </c>
       <c r="G133">
-        <v>0.2531699951003226</v>
+        <v>0.2666666666666667</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -16096,7 +16096,7 @@
         <v>0.2857142857142856</v>
       </c>
       <c r="G134">
-        <v>0.5345092286010409</v>
+        <v>0.555952380952381</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -16119,7 +16119,7 @@
         <v>0.2857142857142856</v>
       </c>
       <c r="G135">
-        <v>0.5345092286010409</v>
+        <v>0.555952380952381</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -16142,7 +16142,7 @@
         <v>-0.3928571428571427</v>
       </c>
       <c r="G136">
-        <v>0.3833168704269727</v>
+        <v>0.3956349206349206</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -16165,7 +16165,7 @@
         <v>0.2142857142857142</v>
       </c>
       <c r="G137">
-        <v>0.6445115810207204</v>
+        <v>0.6615079365079365</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -16188,7 +16188,7 @@
         <v>-0.2142857142857142</v>
       </c>
       <c r="G138">
-        <v>0.6445115810207208</v>
+        <v>0.6615079365079365</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -16211,7 +16211,7 @@
         <v>0.5357142857142856</v>
       </c>
       <c r="G139">
-        <v>0.215217455678013</v>
+        <v>0.2357142857142857</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -16234,7 +16234,7 @@
         <v>-0.7857142857142855</v>
       </c>
       <c r="G140">
-        <v>0.03623846267982718</v>
+        <v>0.04801587301587302</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -16257,7 +16257,7 @@
         <v>-0.07142857142857141</v>
       </c>
       <c r="G141">
-        <v>0.8790481931481541</v>
+        <v>0.9063492063492063</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -16280,7 +16280,7 @@
         <v>0.3571428571428571</v>
       </c>
       <c r="G142">
-        <v>0.4316113520383283</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -16303,7 +16303,7 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="G143">
-        <v>0.7599453002180929</v>
+        <v>0.7825396825396825</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -16326,7 +16326,7 @@
         <v>-0.1071428571428571</v>
       </c>
       <c r="G144">
-        <v>0.8191508555699912</v>
+        <v>0.8396825396825397</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -16349,7 +16349,7 @@
         <v>-0.607142857142857</v>
       </c>
       <c r="G145">
-        <v>0.1482311614811614</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -16372,7 +16372,7 @@
         <v>0.2857142857142856</v>
       </c>
       <c r="G146">
-        <v>0.5345092286010409</v>
+        <v>0.555952380952381</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -16395,7 +16395,7 @@
         <v>0.607142857142857</v>
       </c>
       <c r="G147">
-        <v>0.1482311614811615</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -16418,7 +16418,7 @@
         <v>-0.9285714285714283</v>
       </c>
       <c r="G148">
-        <v>0.002519472403794723</v>
+        <v>0.006746031746031746</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -16441,7 +16441,7 @@
         <v>0.3928571428571427</v>
       </c>
       <c r="G149">
-        <v>0.3833168704269728</v>
+        <v>0.3956349206349206</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -16464,7 +16464,7 @@
         <v>0.07142857142857141</v>
       </c>
       <c r="G150">
-        <v>0.8790481931481541</v>
+        <v>0.9063492063492063</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -16487,7 +16487,7 @@
         <v>0.7857142857142855</v>
       </c>
       <c r="G151">
-        <v>0.03623846267982733</v>
+        <v>0.04801587301587302</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -16510,7 +16510,7 @@
         <v>-0.03571428571428571</v>
       </c>
       <c r="G152">
-        <v>0.9394082054712853</v>
+        <v>0.9634920634920635</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -16533,7 +16533,7 @@
         <v>0.03571428571428571</v>
       </c>
       <c r="G153">
-        <v>0.9394082054712856</v>
+        <v>0.9634920634920635</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -16556,7 +16556,7 @@
         <v>0.5714285714285713</v>
       </c>
       <c r="G154">
-        <v>0.1802019889115277</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -16602,7 +16602,7 @@
         <v>-0.3928571428571427</v>
       </c>
       <c r="G156">
-        <v>0.3833168704269727</v>
+        <v>0.3956349206349206</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -16625,7 +16625,7 @@
         <v>-0.7857142857142855</v>
       </c>
       <c r="G157">
-        <v>0.03623846267982718</v>
+        <v>0.04801587301587302</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -16648,7 +16648,7 @@
         <v>0.5714285714285713</v>
       </c>
       <c r="G158">
-        <v>0.1802019889115277</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -16671,7 +16671,7 @@
         <v>0.4642857142857141</v>
       </c>
       <c r="G159">
-        <v>0.2939341076002518</v>
+        <v>0.3023809523809524</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -16694,7 +16694,7 @@
         <v>-0.5357142857142856</v>
       </c>
       <c r="G160">
-        <v>0.2152174556780128</v>
+        <v>0.2357142857142857</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -16717,7 +16717,7 @@
         <v>0.5357142857142856</v>
       </c>
       <c r="G161">
-        <v>0.215217455678013</v>
+        <v>0.2357142857142857</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -16740,7 +16740,7 @@
         <v>-0.2499999999999999</v>
       </c>
       <c r="G162">
-        <v>0.5887244480896832</v>
+        <v>0.5948412698412698</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -16763,7 +16763,7 @@
         <v>0.7499999999999998</v>
       </c>
       <c r="G163">
-        <v>0.05218140045705796</v>
+        <v>0.06626984126984127</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -16786,7 +16786,7 @@
         <v>-0.4642857142857141</v>
       </c>
       <c r="G164">
-        <v>0.2939341076002521</v>
+        <v>0.3023809523809524</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -16809,7 +16809,7 @@
         <v>-0.1785714285714285</v>
       </c>
       <c r="G165">
-        <v>0.7016579425162729</v>
+        <v>0.7130952380952381</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -16832,7 +16832,7 @@
         <v>0.6428571428571427</v>
       </c>
       <c r="G166">
-        <v>0.1193923734274112</v>
+        <v>0.1388888888888889</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -16855,7 +16855,7 @@
         <v>-0.1071428571428571</v>
       </c>
       <c r="G167">
-        <v>0.8191508555699912</v>
+        <v>0.8396825396825397</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -16878,7 +16878,7 @@
         <v>-0.3928571428571427</v>
       </c>
       <c r="G168">
-        <v>0.3833168704269727</v>
+        <v>0.3956349206349206</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -16901,7 +16901,7 @@
         <v>-0.7142857142857142</v>
       </c>
       <c r="G169">
-        <v>0.07134356146753777</v>
+        <v>0.0880952380952381</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -16924,7 +16924,7 @@
         <v>-0.5714285714285713</v>
       </c>
       <c r="G170">
-        <v>0.1802019889115277</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -16947,7 +16947,7 @@
         <v>-0.2142857142857142</v>
       </c>
       <c r="G171">
-        <v>0.6445115810207208</v>
+        <v>0.6615079365079365</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -16970,7 +16970,7 @@
         <v>-0.3571428571428571</v>
       </c>
       <c r="G172">
-        <v>0.4316113520383278</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -16993,7 +16993,7 @@
         <v>-0.5357142857142856</v>
       </c>
       <c r="G173">
-        <v>0.2152174556780128</v>
+        <v>0.2357142857142857</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -17016,7 +17016,7 @@
         <v>0.4285714285714284</v>
       </c>
       <c r="G174">
-        <v>0.337368311085824</v>
+        <v>0.3535714285714286</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -17039,7 +17039,7 @@
         <v>-0.3928571428571427</v>
       </c>
       <c r="G175">
-        <v>0.3833168704269727</v>
+        <v>0.3956349206349206</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -17062,7 +17062,7 @@
         <v>0.2142857142857142</v>
       </c>
       <c r="G176">
-        <v>0.6445115810207204</v>
+        <v>0.6615079365079365</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -17085,7 +17085,7 @@
         <v>0.4285714285714284</v>
       </c>
       <c r="G177">
-        <v>0.337368311085824</v>
+        <v>0.3535714285714286</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -17131,7 +17131,7 @@
         <v>0.3214285714285713</v>
       </c>
       <c r="G179">
-        <v>0.4820720382996777</v>
+        <v>0.4976190476190476</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -17154,7 +17154,7 @@
         <v>0.4285714285714284</v>
       </c>
       <c r="G180">
-        <v>0.337368311085824</v>
+        <v>0.3535714285714286</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -17177,7 +17177,7 @@
         <v>0.03571428571428571</v>
       </c>
       <c r="G181">
-        <v>0.9394082054712856</v>
+        <v>0.9634920634920635</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -17200,7 +17200,7 @@
         <v>-0.5585812268712466</v>
       </c>
       <c r="G182">
-        <v>0.1924525318805224</v>
+        <v>0.2055555555555555</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -17223,7 +17223,7 @@
         <v>-0.2702812388086677</v>
       </c>
       <c r="G183">
-        <v>0.5577307488053698</v>
+        <v>0.5507936507936508</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -17246,7 +17246,7 @@
         <v>-0.2882999880625788</v>
       </c>
       <c r="G184">
-        <v>0.5306506599466652</v>
+        <v>0.5246031746031746</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -17269,7 +17269,7 @@
         <v>-0.5585812268712466</v>
       </c>
       <c r="G185">
-        <v>0.1924525318805224</v>
+        <v>0.2055555555555555</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -17292,7 +17292,7 @@
         <v>0.4144312328399571</v>
       </c>
       <c r="G186">
-        <v>0.3552689437660521</v>
+        <v>0.3555555555555556</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -17315,7 +17315,7 @@
         <v>-0.4504687313477794</v>
       </c>
       <c r="G187">
-        <v>0.3104293018513228</v>
+        <v>0.3111111111111111</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -17338,7 +17338,7 @@
         <v>0.1982062417930229</v>
       </c>
       <c r="G188">
-        <v>0.6700850339168269</v>
+        <v>0.6674603174603174</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -17361,7 +17361,7 @@
         <v>0.4144312328399571</v>
       </c>
       <c r="G189">
-        <v>0.3552689437660521</v>
+        <v>0.3555555555555556</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -17384,7 +17384,7 @@
         <v>0.01801874925391118</v>
       </c>
       <c r="G190">
-        <v>0.9694153868031987</v>
+        <v>0.9880952380952381</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -17407,7 +17407,7 @@
         <v>0.30631873731649</v>
       </c>
       <c r="G191">
-        <v>0.5040270086665882</v>
+        <v>0.5007936507936508</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -17430,7 +17430,7 @@
         <v>0.4504687313477794</v>
       </c>
       <c r="G192">
-        <v>0.3104293018513229</v>
+        <v>0.3111111111111111</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -17453,7 +17453,7 @@
         <v>0.07207499701564471</v>
       </c>
       <c r="G193">
-        <v>0.8779592508225129</v>
+        <v>0.8873015873015873</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -17476,7 +17476,7 @@
         <v>-0.2499999999999999</v>
       </c>
       <c r="G194">
-        <v>0.5887244480896832</v>
+        <v>0.5948412698412698</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -17499,7 +17499,7 @@
         <v>0.3214285714285713</v>
       </c>
       <c r="G195">
-        <v>0.4820720382996777</v>
+        <v>0.4976190476190476</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -17522,7 +17522,7 @@
         <v>-0.1071428571428571</v>
       </c>
       <c r="G196">
-        <v>0.8191508555699912</v>
+        <v>0.8396825396825397</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -17545,7 +17545,7 @@
         <v>-0.2142857142857142</v>
       </c>
       <c r="G197">
-        <v>0.6445115810207208</v>
+        <v>0.6615079365079365</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -17568,7 +17568,7 @@
         <v>0.4642857142857141</v>
       </c>
       <c r="G198">
-        <v>0.2939341076002518</v>
+        <v>0.3023809523809524</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -17591,7 +17591,7 @@
         <v>0.1785714285714285</v>
       </c>
       <c r="G199">
-        <v>0.7016579425162729</v>
+        <v>0.7130952380952381</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -17614,7 +17614,7 @@
         <v>0.607142857142857</v>
       </c>
       <c r="G200">
-        <v>0.1482311614811615</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -17637,7 +17637,7 @@
         <v>0.1071428571428571</v>
       </c>
       <c r="G201">
-        <v>0.8191508555699913</v>
+        <v>0.8396825396825397</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -17660,7 +17660,7 @@
         <v>-0.3214285714285713</v>
       </c>
       <c r="G202">
-        <v>0.4820720382996777</v>
+        <v>0.4976190476190476</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -17683,7 +17683,7 @@
         <v>0.07142857142857141</v>
       </c>
       <c r="G203">
-        <v>0.8790481931481541</v>
+        <v>0.9063492063492063</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -17706,7 +17706,7 @@
         <v>-0.3571428571428571</v>
       </c>
       <c r="G204">
-        <v>0.4316113520383278</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -17729,7 +17729,7 @@
         <v>-0.07142857142857141</v>
       </c>
       <c r="G205">
-        <v>0.8790481931481541</v>
+        <v>0.9063492063492063</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -17752,7 +17752,7 @@
         <v>-0.3571428571428571</v>
       </c>
       <c r="G206">
-        <v>0.4316113520383278</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -17775,7 +17775,7 @@
         <v>0.5357142857142856</v>
       </c>
       <c r="G207">
-        <v>0.215217455678013</v>
+        <v>0.2357142857142857</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -17798,7 +17798,7 @@
         <v>-0.6785714285714284</v>
       </c>
       <c r="G208">
-        <v>0.09375025395983154</v>
+        <v>0.1095238095238095</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -17821,7 +17821,7 @@
         <v>-0.3214285714285713</v>
       </c>
       <c r="G209">
-        <v>0.4820720382996777</v>
+        <v>0.4976190476190476</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -17844,7 +17844,7 @@
         <v>0.607142857142857</v>
       </c>
       <c r="G210">
-        <v>0.1482311614811615</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -17867,7 +17867,7 @@
         <v>0.3928571428571427</v>
       </c>
       <c r="G211">
-        <v>0.3833168704269728</v>
+        <v>0.3956349206349206</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -17890,7 +17890,7 @@
         <v>-0.3928571428571427</v>
       </c>
       <c r="G212">
-        <v>0.3833168704269727</v>
+        <v>0.3956349206349206</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -17913,7 +17913,7 @@
         <v>0.6785714285714284</v>
       </c>
       <c r="G213">
-        <v>0.09375025395983154</v>
+        <v>0.1095238095238095</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -17936,7 +17936,7 @@
         <v>0.2857142857142856</v>
       </c>
       <c r="G214">
-        <v>0.5345092286010409</v>
+        <v>0.555952380952381</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -17959,7 +17959,7 @@
         <v>0.6785714285714284</v>
       </c>
       <c r="G215">
-        <v>0.09375025395983154</v>
+        <v>0.1095238095238095</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -17982,7 +17982,7 @@
         <v>-0.1785714285714285</v>
       </c>
       <c r="G216">
-        <v>0.7016579425162729</v>
+        <v>0.7130952380952381</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -18005,7 +18005,7 @@
         <v>-0.7857142857142855</v>
       </c>
       <c r="G217">
-        <v>0.03623846267982718</v>
+        <v>0.04801587301587302</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -18028,7 +18028,7 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="G218">
-        <v>0.7871720116618075</v>
+        <v>0.8027777777777778</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -18051,7 +18051,7 @@
         <v>0.4857142857142857</v>
       </c>
       <c r="G219">
-        <v>0.3287230320699709</v>
+        <v>0.3555555555555556</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -18074,7 +18074,7 @@
         <v>0.02857142857142857</v>
       </c>
       <c r="G220">
-        <v>0.9571545189504373</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -18097,7 +18097,7 @@
         <v>0.2</v>
       </c>
       <c r="G221">
-        <v>0.7040000000000001</v>
+        <v>0.7138888888888889</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -18120,7 +18120,7 @@
         <v>-0.02857142857142857</v>
       </c>
       <c r="G222">
-        <v>0.9571545189504375</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -18143,7 +18143,7 @@
         <v>0.6</v>
       </c>
       <c r="G223">
-        <v>0.2079999999999998</v>
+        <v>0.2416666666666667</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -18166,7 +18166,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="G224">
-        <v>0.3965014577259475</v>
+        <v>0.4194444444444445</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -18189,7 +18189,7 @@
         <v>-0.2571428571428572</v>
       </c>
       <c r="G225">
-        <v>0.6227871720116618</v>
+        <v>0.6583333333333333</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -18212,7 +18212,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="G226">
-        <v>0.3965014577259475</v>
+        <v>0.4194444444444445</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -18235,7 +18235,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="G227">
-        <v>0.7871720116618076</v>
+        <v>0.8027777777777778</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -18258,7 +18258,7 @@
         <v>-0.6</v>
       </c>
       <c r="G228">
-        <v>0.2079999999999997</v>
+        <v>0.2416666666666667</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -18281,7 +18281,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="G229">
-        <v>0.7871720116618076</v>
+        <v>0.8027777777777778</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -18304,7 +18304,7 @@
         <v>0.4285714285714284</v>
       </c>
       <c r="G230">
-        <v>0.337368311085824</v>
+        <v>0.3535714285714286</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -18327,7 +18327,7 @@
         <v>0.3214285714285713</v>
       </c>
       <c r="G231">
-        <v>0.4820720382996777</v>
+        <v>0.4976190476190476</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -18350,7 +18350,7 @@
         <v>-0.6428571428571427</v>
       </c>
       <c r="G232">
-        <v>0.1193923734274112</v>
+        <v>0.1388888888888889</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -18373,7 +18373,7 @@
         <v>0.607142857142857</v>
       </c>
       <c r="G233">
-        <v>0.1482311614811615</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -18396,7 +18396,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="G234">
-        <v>0.7599453002180931</v>
+        <v>0.7825396825396825</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -18419,7 +18419,7 @@
         <v>0.4642857142857141</v>
       </c>
       <c r="G235">
-        <v>0.2939341076002518</v>
+        <v>0.3023809523809524</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -18442,7 +18442,7 @@
         <v>0.3928571428571427</v>
       </c>
       <c r="G236">
-        <v>0.3833168704269728</v>
+        <v>0.3956349206349206</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -18465,7 +18465,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="G237">
-        <v>0.7599453002180931</v>
+        <v>0.7825396825396825</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -18488,7 +18488,7 @@
         <v>0.5714285714285713</v>
       </c>
       <c r="G238">
-        <v>0.1802019889115277</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -18511,7 +18511,7 @@
         <v>-0.3571428571428571</v>
       </c>
       <c r="G239">
-        <v>0.4316113520383278</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -18534,7 +18534,7 @@
         <v>-0.2857142857142856</v>
       </c>
       <c r="G240">
-        <v>0.5345092286010411</v>
+        <v>0.555952380952381</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -18557,7 +18557,7 @@
         <v>-0.3214285714285713</v>
       </c>
       <c r="G241">
-        <v>0.4820720382996777</v>
+        <v>0.4976190476190476</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -18580,7 +18580,7 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="G242">
-        <v>0.7599453002180929</v>
+        <v>0.7825396825396825</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -18603,7 +18603,7 @@
         <v>-0.3571428571428571</v>
       </c>
       <c r="G243">
-        <v>0.4316113520383278</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -18626,7 +18626,7 @@
         <v>-0.6428571428571427</v>
       </c>
       <c r="G244">
-        <v>0.1193923734274112</v>
+        <v>0.1388888888888889</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -18649,7 +18649,7 @@
         <v>-0.07142857142857141</v>
       </c>
       <c r="G245">
-        <v>0.8790481931481541</v>
+        <v>0.9063492063492063</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -18672,7 +18672,7 @@
         <v>0.8214285714285713</v>
       </c>
       <c r="G246">
-        <v>0.02344880834569154</v>
+        <v>0.03412698412698412</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -18695,7 +18695,7 @@
         <v>0.2857142857142856</v>
       </c>
       <c r="G247">
-        <v>0.5345092286010409</v>
+        <v>0.555952380952381</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -18718,7 +18718,7 @@
         <v>0.4642857142857141</v>
       </c>
       <c r="G248">
-        <v>0.2939341076002518</v>
+        <v>0.3023809523809524</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -18741,7 +18741,7 @@
         <v>-0.4285714285714284</v>
       </c>
       <c r="G249">
-        <v>0.3373683110858242</v>
+        <v>0.3535714285714286</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -18764,7 +18764,7 @@
         <v>0.5714285714285713</v>
       </c>
       <c r="G250">
-        <v>0.1802019889115277</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -18787,7 +18787,7 @@
         <v>-0.3571428571428571</v>
       </c>
       <c r="G251">
-        <v>0.4316113520383278</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -18810,7 +18810,7 @@
         <v>-0.03571428571428571</v>
       </c>
       <c r="G252">
-        <v>0.9394082054712853</v>
+        <v>0.9634920634920635</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -18833,7 +18833,7 @@
         <v>-0.07142857142857141</v>
       </c>
       <c r="G253">
-        <v>0.8790481931481541</v>
+        <v>0.9063492063492063</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -18856,7 +18856,7 @@
         <v>0.3571428571428571</v>
       </c>
       <c r="G254">
-        <v>0.4316113520383283</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -18879,7 +18879,7 @@
         <v>0.1785714285714285</v>
       </c>
       <c r="G255">
-        <v>0.7016579425162729</v>
+        <v>0.7130952380952381</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -18902,7 +18902,7 @@
         <v>-0.2857142857142856</v>
       </c>
       <c r="G256">
-        <v>0.5345092286010411</v>
+        <v>0.555952380952381</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -18925,7 +18925,7 @@
         <v>0.4642857142857141</v>
       </c>
       <c r="G257">
-        <v>0.2939341076002518</v>
+        <v>0.3023809523809524</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -18948,7 +18948,7 @@
         <v>0.4285714285714284</v>
       </c>
       <c r="G258">
-        <v>0.337368311085824</v>
+        <v>0.3535714285714286</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -18971,7 +18971,7 @@
         <v>0.3214285714285713</v>
       </c>
       <c r="G259">
-        <v>0.4820720382996777</v>
+        <v>0.4976190476190476</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -18994,7 +18994,7 @@
         <v>0.2857142857142856</v>
       </c>
       <c r="G260">
-        <v>0.5345092286010409</v>
+        <v>0.555952380952381</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -19017,7 +19017,7 @@
         <v>0.03571428571428571</v>
       </c>
       <c r="G261">
-        <v>0.9394082054712856</v>
+        <v>0.9634920634920635</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -19040,7 +19040,7 @@
         <v>0.1785714285714285</v>
       </c>
       <c r="G262">
-        <v>0.7016579425162729</v>
+        <v>0.7130952380952381</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -19063,7 +19063,7 @@
         <v>0.1785714285714285</v>
       </c>
       <c r="G263">
-        <v>0.7016579425162729</v>
+        <v>0.7130952380952381</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -19086,7 +19086,7 @@
         <v>-0.5357142857142856</v>
       </c>
       <c r="G264">
-        <v>0.2152174556780128</v>
+        <v>0.2357142857142857</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -19109,7 +19109,7 @@
         <v>-0.3928571428571427</v>
       </c>
       <c r="G265">
-        <v>0.3833168704269727</v>
+        <v>0.3956349206349206</v>
       </c>
     </row>
     <row r="266" spans="1:7">
@@ -19132,7 +19132,7 @@
         <v>0.2857142857142856</v>
       </c>
       <c r="G266">
-        <v>0.5345092286010409</v>
+        <v>0.555952380952381</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -19155,7 +19155,7 @@
         <v>-0.1785714285714285</v>
       </c>
       <c r="G267">
-        <v>0.7016579425162729</v>
+        <v>0.7130952380952381</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -19178,7 +19178,7 @@
         <v>-0.4999999999999999</v>
       </c>
       <c r="G268">
-        <v>0.2531699951003226</v>
+        <v>0.2666666666666667</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -19201,7 +19201,7 @@
         <v>-0.03571428571428571</v>
       </c>
       <c r="G269">
-        <v>0.9394082054712853</v>
+        <v>0.9634920634920635</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -19224,7 +19224,7 @@
         <v>0.2857142857142856</v>
       </c>
       <c r="G270">
-        <v>0.5345092286010409</v>
+        <v>0.555952380952381</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -19247,7 +19247,7 @@
         <v>0.1785714285714285</v>
       </c>
       <c r="G271">
-        <v>0.7016579425162729</v>
+        <v>0.7130952380952381</v>
       </c>
     </row>
     <row r="272" spans="1:7">
@@ -19270,7 +19270,7 @@
         <v>0.4285714285714284</v>
       </c>
       <c r="G272">
-        <v>0.337368311085824</v>
+        <v>0.3535714285714286</v>
       </c>
     </row>
     <row r="273" spans="1:7">
@@ -19293,7 +19293,7 @@
         <v>0.03571428571428571</v>
       </c>
       <c r="G273">
-        <v>0.9394082054712856</v>
+        <v>0.9634920634920635</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -19316,7 +19316,7 @@
         <v>0.5357142857142856</v>
       </c>
       <c r="G274">
-        <v>0.215217455678013</v>
+        <v>0.2357142857142857</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -19339,7 +19339,7 @@
         <v>-0.1785714285714285</v>
       </c>
       <c r="G275">
-        <v>0.7016579425162729</v>
+        <v>0.7130952380952381</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -19362,7 +19362,7 @@
         <v>0.1785714285714285</v>
       </c>
       <c r="G276">
-        <v>0.7016579425162729</v>
+        <v>0.7130952380952381</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -19385,7 +19385,7 @@
         <v>-0.4642857142857141</v>
       </c>
       <c r="G277">
-        <v>0.2939341076002521</v>
+        <v>0.3023809523809524</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -19408,7 +19408,7 @@
         <v>0.2142857142857142</v>
       </c>
       <c r="G278">
-        <v>0.6445115810207204</v>
+        <v>0.6615079365079365</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -19431,7 +19431,7 @@
         <v>0.1071428571428571</v>
       </c>
       <c r="G279">
-        <v>0.8191508555699913</v>
+        <v>0.8396825396825397</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -19454,7 +19454,7 @@
         <v>-0.3214285714285713</v>
       </c>
       <c r="G280">
-        <v>0.4820720382996777</v>
+        <v>0.4976190476190476</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -19477,7 +19477,7 @@
         <v>0.3928571428571427</v>
       </c>
       <c r="G281">
-        <v>0.3833168704269728</v>
+        <v>0.3956349206349206</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -19500,7 +19500,7 @@
         <v>0.4642857142857141</v>
       </c>
       <c r="G282">
-        <v>0.2939341076002518</v>
+        <v>0.3023809523809524</v>
       </c>
     </row>
     <row r="283" spans="1:7">
@@ -19523,7 +19523,7 @@
         <v>0.2142857142857142</v>
       </c>
       <c r="G283">
-        <v>0.6445115810207204</v>
+        <v>0.6615079365079365</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -19546,7 +19546,7 @@
         <v>0.3214285714285713</v>
       </c>
       <c r="G284">
-        <v>0.4820720382996777</v>
+        <v>0.4976190476190476</v>
       </c>
     </row>
     <row r="285" spans="1:7">
@@ -19569,7 +19569,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="G285">
-        <v>0.7599453002180931</v>
+        <v>0.7825396825396825</v>
       </c>
     </row>
     <row r="286" spans="1:7">
@@ -19592,7 +19592,7 @@
         <v>0.2142857142857142</v>
       </c>
       <c r="G286">
-        <v>0.6445115810207204</v>
+        <v>0.6615079365079365</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -19615,7 +19615,7 @@
         <v>0.1071428571428571</v>
       </c>
       <c r="G287">
-        <v>0.8191508555699913</v>
+        <v>0.8396825396825397</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -19638,7 +19638,7 @@
         <v>-0.3571428571428571</v>
       </c>
       <c r="G288">
-        <v>0.4316113520383278</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -19661,7 +19661,7 @@
         <v>-0.3214285714285713</v>
       </c>
       <c r="G289">
-        <v>0.4820720382996777</v>
+        <v>0.4976190476190476</v>
       </c>
     </row>
     <row r="290" spans="1:7">
@@ -19684,7 +19684,7 @@
         <v>0.3571428571428571</v>
       </c>
       <c r="G290">
-        <v>0.4316113520383283</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="291" spans="1:7">
@@ -19707,7 +19707,7 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="G291">
-        <v>0.7599453002180929</v>
+        <v>0.7825396825396825</v>
       </c>
     </row>
     <row r="292" spans="1:7">
@@ -19730,7 +19730,7 @@
         <v>0.2142857142857142</v>
       </c>
       <c r="G292">
-        <v>0.6445115810207204</v>
+        <v>0.6615079365079365</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -19753,7 +19753,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="G293">
-        <v>0.7599453002180931</v>
+        <v>0.7825396825396825</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -19776,7 +19776,7 @@
         <v>-0.7499999999999998</v>
       </c>
       <c r="G294">
-        <v>0.05218140045705796</v>
+        <v>0.06626984126984127</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -19799,7 +19799,7 @@
         <v>0.07142857142857141</v>
       </c>
       <c r="G295">
-        <v>0.8790481931481541</v>
+        <v>0.9063492063492063</v>
       </c>
     </row>
     <row r="296" spans="1:7">
@@ -19822,7 +19822,7 @@
         <v>-0.2499999999999999</v>
       </c>
       <c r="G296">
-        <v>0.5887244480896832</v>
+        <v>0.5948412698412698</v>
       </c>
     </row>
     <row r="297" spans="1:7">
@@ -19845,7 +19845,7 @@
         <v>0.7142857142857142</v>
       </c>
       <c r="G297">
-        <v>0.07134356146753777</v>
+        <v>0.0880952380952381</v>
       </c>
     </row>
     <row r="298" spans="1:7">
@@ -19868,7 +19868,7 @@
         <v>0.07142857142857141</v>
       </c>
       <c r="G298">
-        <v>0.8790481931481541</v>
+        <v>0.9063492063492063</v>
       </c>
     </row>
     <row r="299" spans="1:7">
@@ -19891,7 +19891,7 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="G299">
-        <v>0.7599453002180929</v>
+        <v>0.7825396825396825</v>
       </c>
     </row>
     <row r="300" spans="1:7">
@@ -19914,7 +19914,7 @@
         <v>0.3928571428571427</v>
       </c>
       <c r="G300">
-        <v>0.3833168704269728</v>
+        <v>0.3956349206349206</v>
       </c>
     </row>
     <row r="301" spans="1:7">
@@ -19937,7 +19937,7 @@
         <v>-0.5714285714285713</v>
       </c>
       <c r="G301">
-        <v>0.1802019889115277</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="302" spans="1:7">
@@ -19960,7 +19960,7 @@
         <v>0.3243374865704012</v>
       </c>
       <c r="G302">
-        <v>0.4778854797399308</v>
+        <v>0.4746031746031746</v>
       </c>
     </row>
     <row r="303" spans="1:7">
@@ -19983,7 +19983,7 @@
         <v>0.2162249910469341</v>
       </c>
       <c r="G303">
-        <v>0.6414455093539178</v>
+        <v>0.6357142857142857</v>
       </c>
     </row>
     <row r="304" spans="1:7">
@@ -20006,7 +20006,7 @@
         <v>0.3603749850782236</v>
       </c>
       <c r="G304">
-        <v>0.4271488085609063</v>
+        <v>0.4261904761904762</v>
       </c>
     </row>
     <row r="305" spans="1:7">
@@ -20029,7 +20029,7 @@
         <v>-0.07207499701564471</v>
       </c>
       <c r="G305">
-        <v>0.8779592508225129</v>
+        <v>0.8873015873015873</v>
       </c>
     </row>
     <row r="306" spans="1:7">
@@ -20052,7 +20052,7 @@
         <v>-0.7748062179181806</v>
       </c>
       <c r="G306">
-        <v>0.04076946252042032</v>
+        <v>0.05079365079365079</v>
       </c>
     </row>
     <row r="307" spans="1:7">
@@ -20075,7 +20075,7 @@
         <v>0.1081124955234671</v>
       </c>
       <c r="G307">
-        <v>0.8175332656241185</v>
+        <v>0.8222222222222222</v>
       </c>
     </row>
     <row r="308" spans="1:7">
@@ -20098,7 +20098,7 @@
         <v>-0.4504687313477794</v>
       </c>
       <c r="G308">
-        <v>0.3104293018513228</v>
+        <v>0.3111111111111111</v>
       </c>
     </row>
     <row r="309" spans="1:7">
@@ -20121,7 +20121,7 @@
         <v>0.6306562238868911</v>
       </c>
       <c r="G309">
-        <v>0.1288876956849579</v>
+        <v>0.1436507936507936</v>
       </c>
     </row>
     <row r="310" spans="1:7">
@@ -20144,7 +20144,7 @@
         <v>-0.05405624776173353</v>
       </c>
       <c r="G310">
-        <v>0.9083652825239956</v>
+        <v>0.919047619047619</v>
       </c>
     </row>
     <row r="311" spans="1:7">
@@ -20167,7 +20167,7 @@
         <v>0.2162249910469341</v>
       </c>
       <c r="G311">
-        <v>0.6414455093539178</v>
+        <v>0.6357142857142857</v>
       </c>
     </row>
     <row r="312" spans="1:7">
@@ -20190,7 +20190,7 @@
         <v>0.3243374865704012</v>
       </c>
       <c r="G312">
-        <v>0.4778854797399308</v>
+        <v>0.4746031746031746</v>
       </c>
     </row>
     <row r="313" spans="1:7">
@@ -20213,7 +20213,7 @@
         <v>-0.4865062298556018</v>
       </c>
       <c r="G313">
-        <v>0.268248562317831</v>
+        <v>0.273015873015873</v>
       </c>
     </row>
     <row r="314" spans="1:7">
@@ -20236,7 +20236,7 @@
         <v>0.2142857142857142</v>
       </c>
       <c r="G314">
-        <v>0.6445115810207204</v>
+        <v>0.6615079365079365</v>
       </c>
     </row>
     <row r="315" spans="1:7">
@@ -20259,7 +20259,7 @@
         <v>-0.3928571428571427</v>
       </c>
       <c r="G315">
-        <v>0.3833168704269727</v>
+        <v>0.3956349206349206</v>
       </c>
     </row>
     <row r="316" spans="1:7">
@@ -20282,7 +20282,7 @@
         <v>-0.2142857142857142</v>
       </c>
       <c r="G316">
-        <v>0.6445115810207208</v>
+        <v>0.6615079365079365</v>
       </c>
     </row>
     <row r="317" spans="1:7">
@@ -20305,7 +20305,7 @@
         <v>-0.2499999999999999</v>
       </c>
       <c r="G317">
-        <v>0.5887244480896832</v>
+        <v>0.5948412698412698</v>
       </c>
     </row>
     <row r="318" spans="1:7">
@@ -20328,7 +20328,7 @@
         <v>0.2142857142857142</v>
       </c>
       <c r="G318">
-        <v>0.6445115810207204</v>
+        <v>0.6615079365079365</v>
       </c>
     </row>
     <row r="319" spans="1:7">
@@ -20351,7 +20351,7 @@
         <v>0.3214285714285713</v>
       </c>
       <c r="G319">
-        <v>0.4820720382996777</v>
+        <v>0.4976190476190476</v>
       </c>
     </row>
     <row r="320" spans="1:7">
@@ -20374,7 +20374,7 @@
         <v>-0.2142857142857142</v>
       </c>
       <c r="G320">
-        <v>0.6445115810207208</v>
+        <v>0.6615079365079365</v>
       </c>
     </row>
     <row r="321" spans="1:7">
@@ -20397,7 +20397,7 @@
         <v>-0.2142857142857142</v>
       </c>
       <c r="G321">
-        <v>0.6445115810207208</v>
+        <v>0.6615079365079365</v>
       </c>
     </row>
     <row r="322" spans="1:7">
@@ -20420,7 +20420,7 @@
         <v>0.3571428571428571</v>
       </c>
       <c r="G322">
-        <v>0.4316113520383283</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="323" spans="1:7">
@@ -20443,7 +20443,7 @@
         <v>-0.3928571428571427</v>
       </c>
       <c r="G323">
-        <v>0.3833168704269727</v>
+        <v>0.3956349206349206</v>
       </c>
     </row>
     <row r="324" spans="1:7">
@@ -20466,7 +20466,7 @@
         <v>0.2857142857142856</v>
       </c>
       <c r="G324">
-        <v>0.5345092286010409</v>
+        <v>0.555952380952381</v>
       </c>
     </row>
     <row r="325" spans="1:7">
@@ -20489,7 +20489,7 @@
         <v>0.07142857142857141</v>
       </c>
       <c r="G325">
-        <v>0.8790481931481541</v>
+        <v>0.9063492063492063</v>
       </c>
     </row>
     <row r="326" spans="1:7">
@@ -20512,7 +20512,7 @@
         <v>0.6428571428571427</v>
       </c>
       <c r="G326">
-        <v>0.1193923734274112</v>
+        <v>0.1388888888888889</v>
       </c>
     </row>
     <row r="327" spans="1:7">
@@ -20535,7 +20535,7 @@
         <v>-0.1071428571428571</v>
       </c>
       <c r="G327">
-        <v>0.8191508555699912</v>
+        <v>0.8396825396825397</v>
       </c>
     </row>
     <row r="328" spans="1:7">
@@ -20558,7 +20558,7 @@
         <v>-0.3214285714285713</v>
       </c>
       <c r="G328">
-        <v>0.4820720382996777</v>
+        <v>0.4976190476190476</v>
       </c>
     </row>
     <row r="329" spans="1:7">
@@ -20581,7 +20581,7 @@
         <v>0.03571428571428571</v>
       </c>
       <c r="G329">
-        <v>0.9394082054712856</v>
+        <v>0.9634920634920635</v>
       </c>
     </row>
     <row r="330" spans="1:7">
@@ -20604,7 +20604,7 @@
         <v>-0.1785714285714285</v>
       </c>
       <c r="G330">
-        <v>0.7016579425162729</v>
+        <v>0.7130952380952381</v>
       </c>
     </row>
     <row r="331" spans="1:7">
@@ -20627,7 +20627,7 @@
         <v>0.2857142857142856</v>
       </c>
       <c r="G331">
-        <v>0.5345092286010409</v>
+        <v>0.555952380952381</v>
       </c>
     </row>
     <row r="332" spans="1:7">
@@ -20650,7 +20650,7 @@
         <v>0.2499999999999999</v>
       </c>
       <c r="G332">
-        <v>0.5887244480896832</v>
+        <v>0.5948412698412698</v>
       </c>
     </row>
     <row r="333" spans="1:7">
@@ -20673,7 +20673,7 @@
         <v>0.7142857142857142</v>
       </c>
       <c r="G333">
-        <v>0.07134356146753777</v>
+        <v>0.0880952380952381</v>
       </c>
     </row>
     <row r="334" spans="1:7">
@@ -20696,7 +20696,7 @@
         <v>0.3571428571428571</v>
       </c>
       <c r="G334">
-        <v>0.4316113520383283</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="335" spans="1:7">
@@ -20719,7 +20719,7 @@
         <v>-0.1071428571428571</v>
       </c>
       <c r="G335">
-        <v>0.8191508555699912</v>
+        <v>0.8396825396825397</v>
       </c>
     </row>
     <row r="336" spans="1:7">
@@ -20742,7 +20742,7 @@
         <v>-0.07142857142857141</v>
       </c>
       <c r="G336">
-        <v>0.8790481931481541</v>
+        <v>0.9063492063492063</v>
       </c>
     </row>
     <row r="337" spans="1:7">
@@ -20765,7 +20765,7 @@
         <v>-0.5357142857142856</v>
       </c>
       <c r="G337">
-        <v>0.2152174556780128</v>
+        <v>0.2357142857142857</v>
       </c>
     </row>
     <row r="338" spans="1:7">
@@ -20788,7 +20788,7 @@
         <v>-0.2571428571428572</v>
       </c>
       <c r="G338">
-        <v>0.6227871720116618</v>
+        <v>0.6583333333333333</v>
       </c>
     </row>
     <row r="339" spans="1:7">
@@ -20811,7 +20811,7 @@
         <v>-0.3714285714285714</v>
       </c>
       <c r="G339">
-        <v>0.4684781341107874</v>
+        <v>0.4972222222222222</v>
       </c>
     </row>
     <row r="340" spans="1:7">
@@ -20834,7 +20834,7 @@
         <v>0.02857142857142857</v>
       </c>
       <c r="G340">
-        <v>0.9571545189504373</v>
+        <v>1</v>
       </c>
     </row>
     <row r="341" spans="1:7">
@@ -20857,7 +20857,7 @@
         <v>-0.2</v>
       </c>
       <c r="G341">
-        <v>0.7040000000000001</v>
+        <v>0.7138888888888889</v>
       </c>
     </row>
     <row r="342" spans="1:7">
@@ -20880,7 +20880,7 @@
         <v>0.08571428571428572</v>
       </c>
       <c r="G342">
-        <v>0.871743440233236</v>
+        <v>0.9194444444444444</v>
       </c>
     </row>
     <row r="343" spans="1:7">
@@ -20903,7 +20903,7 @@
         <v>-0.08571428571428572</v>
       </c>
       <c r="G343">
-        <v>0.8717434402332366</v>
+        <v>0.9194444444444444</v>
       </c>
     </row>
     <row r="344" spans="1:7">
@@ -20926,7 +20926,7 @@
         <v>-0.2571428571428572</v>
       </c>
       <c r="G344">
-        <v>0.6227871720116618</v>
+        <v>0.6583333333333333</v>
       </c>
     </row>
     <row r="345" spans="1:7">
@@ -20949,7 +20949,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="G345">
-        <v>0.3965014577259475</v>
+        <v>0.4194444444444445</v>
       </c>
     </row>
     <row r="346" spans="1:7">
@@ -20972,7 +20972,7 @@
         <v>-0.02857142857142857</v>
       </c>
       <c r="G346">
-        <v>0.9571545189504375</v>
+        <v>1</v>
       </c>
     </row>
     <row r="347" spans="1:7">
@@ -20995,7 +20995,7 @@
         <v>-0.3714285714285714</v>
       </c>
       <c r="G347">
-        <v>0.4684781341107874</v>
+        <v>0.4972222222222222</v>
       </c>
     </row>
     <row r="348" spans="1:7">
@@ -21018,7 +21018,7 @@
         <v>0.3714285714285714</v>
       </c>
       <c r="G348">
-        <v>0.4684781341107874</v>
+        <v>0.4972222222222222</v>
       </c>
     </row>
     <row r="349" spans="1:7">
@@ -21041,7 +21041,7 @@
         <v>0.4857142857142857</v>
       </c>
       <c r="G349">
-        <v>0.3287230320699709</v>
+        <v>0.3555555555555556</v>
       </c>
     </row>
     <row r="350" spans="1:7">
@@ -21064,7 +21064,7 @@
         <v>-0.2142857142857142</v>
       </c>
       <c r="G350">
-        <v>0.6445115810207208</v>
+        <v>0.6615079365079365</v>
       </c>
     </row>
     <row r="351" spans="1:7">
@@ -21087,7 +21087,7 @@
         <v>-0.3214285714285713</v>
       </c>
       <c r="G351">
-        <v>0.4820720382996777</v>
+        <v>0.4976190476190476</v>
       </c>
     </row>
     <row r="352" spans="1:7">
@@ -21110,7 +21110,7 @@
         <v>-0.2857142857142856</v>
       </c>
       <c r="G352">
-        <v>0.5345092286010411</v>
+        <v>0.555952380952381</v>
       </c>
     </row>
     <row r="353" spans="1:7">
@@ -21133,7 +21133,7 @@
         <v>-0.3928571428571427</v>
       </c>
       <c r="G353">
-        <v>0.3833168704269727</v>
+        <v>0.3956349206349206</v>
       </c>
     </row>
     <row r="354" spans="1:7">
@@ -21156,7 +21156,7 @@
         <v>-0.1071428571428571</v>
       </c>
       <c r="G354">
-        <v>0.8191508555699912</v>
+        <v>0.8396825396825397</v>
       </c>
     </row>
     <row r="355" spans="1:7">
@@ -21179,7 +21179,7 @@
         <v>-0.3214285714285713</v>
       </c>
       <c r="G355">
-        <v>0.4820720382996777</v>
+        <v>0.4976190476190476</v>
       </c>
     </row>
     <row r="356" spans="1:7">
@@ -21202,7 +21202,7 @@
         <v>0.3214285714285713</v>
       </c>
       <c r="G356">
-        <v>0.4820720382996777</v>
+        <v>0.4976190476190476</v>
       </c>
     </row>
     <row r="357" spans="1:7">
@@ -21225,7 +21225,7 @@
         <v>-0.1428571428571428</v>
       </c>
       <c r="G357">
-        <v>0.7599453002180931</v>
+        <v>0.7825396825396825</v>
       </c>
     </row>
     <row r="358" spans="1:7">
@@ -21248,7 +21248,7 @@
         <v>0.3571428571428571</v>
       </c>
       <c r="G358">
-        <v>0.4316113520383283</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="359" spans="1:7">
@@ -21271,7 +21271,7 @@
         <v>-0.3214285714285713</v>
       </c>
       <c r="G359">
-        <v>0.4820720382996777</v>
+        <v>0.4976190476190476</v>
       </c>
     </row>
     <row r="360" spans="1:7">
@@ -21294,7 +21294,7 @@
         <v>0.7857142857142855</v>
       </c>
       <c r="G360">
-        <v>0.03623846267982733</v>
+        <v>0.04801587301587302</v>
       </c>
     </row>
     <row r="361" spans="1:7">
@@ -21317,7 +21317,7 @@
         <v>-0.1071428571428571</v>
       </c>
       <c r="G361">
-        <v>0.8191508555699912</v>
+        <v>0.8396825396825397</v>
       </c>
     </row>
     <row r="362" spans="1:7">
@@ -21340,7 +21340,7 @@
         <v>-0.1428571428571429</v>
       </c>
       <c r="G362">
-        <v>0.7357648598798121</v>
+        <v>0.7520337301587302</v>
       </c>
     </row>
     <row r="363" spans="1:7">
@@ -21363,7 +21363,7 @@
         <v>-0.04761904761904762</v>
       </c>
       <c r="G363">
-        <v>0.9108491685195835</v>
+        <v>0.9348710317460317</v>
       </c>
     </row>
     <row r="364" spans="1:7">
@@ -21386,7 +21386,7 @@
         <v>0.2380952380952381</v>
       </c>
       <c r="G364">
-        <v>0.5701563208157683</v>
+        <v>0.5821428571428572</v>
       </c>
     </row>
     <row r="365" spans="1:7">
@@ -21409,7 +21409,7 @@
         <v>-0.1904761904761905</v>
       </c>
       <c r="G365">
-        <v>0.6514014957024816</v>
+        <v>0.6645833333333333</v>
       </c>
     </row>
     <row r="366" spans="1:7">
@@ -21432,7 +21432,7 @@
         <v>0.2619047619047619</v>
       </c>
       <c r="G366">
-        <v>0.5309228615658013</v>
+        <v>0.5364087301587301</v>
       </c>
     </row>
     <row r="367" spans="1:7">
@@ -21455,7 +21455,7 @@
         <v>-0.1904761904761905</v>
       </c>
       <c r="G367">
-        <v>0.6514014957024816</v>
+        <v>0.6645833333333333</v>
       </c>
     </row>
     <row r="368" spans="1:7">
@@ -21478,7 +21478,7 @@
         <v>-0.6190476190476192</v>
       </c>
       <c r="G368">
-        <v>0.1017330374542645</v>
+        <v>0.1149801587301587</v>
       </c>
     </row>
     <row r="369" spans="1:7">
@@ -21501,7 +21501,7 @@
         <v>0.2857142857142858</v>
       </c>
       <c r="G369">
-        <v>0.4927262450169571</v>
+        <v>0.5007936507936508</v>
       </c>
     </row>
     <row r="370" spans="1:7">
@@ -21524,7 +21524,7 @@
         <v>-0.2380952380952381</v>
       </c>
       <c r="G370">
-        <v>0.5701563208157683</v>
+        <v>0.5821428571428572</v>
       </c>
     </row>
     <row r="371" spans="1:7">
@@ -21547,7 +21547,7 @@
         <v>-0.02380952380952381</v>
       </c>
       <c r="G371">
-        <v>0.9553740118158809</v>
+        <v>0.9767857142857143</v>
       </c>
     </row>
     <row r="372" spans="1:7">
@@ -21570,7 +21570,7 @@
         <v>0.09523809523809525</v>
       </c>
       <c r="G372">
-        <v>0.8225054302036114</v>
+        <v>0.8401289682539682</v>
       </c>
     </row>
     <row r="373" spans="1:7">
@@ -21593,7 +21593,7 @@
         <v>0.2857142857142858</v>
       </c>
       <c r="G373">
-        <v>0.4927262450169571</v>
+        <v>0.5007936507936508</v>
       </c>
     </row>
     <row r="374" spans="1:7">
@@ -21616,7 +21616,7 @@
         <v>-0.4285714285714287</v>
       </c>
       <c r="G374">
-        <v>0.2894032248467901</v>
+        <v>0.2992063492063492</v>
       </c>
     </row>
     <row r="375" spans="1:7">
@@ -21639,7 +21639,7 @@
         <v>0.1904761904761905</v>
       </c>
       <c r="G375">
-        <v>0.6514014957024816</v>
+        <v>0.6645833333333333</v>
       </c>
     </row>
     <row r="376" spans="1:7">
@@ -21662,7 +21662,7 @@
         <v>0.2619047619047619</v>
       </c>
       <c r="G376">
-        <v>0.5309228615658013</v>
+        <v>0.5364087301587301</v>
       </c>
     </row>
     <row r="377" spans="1:7">
@@ -21685,7 +21685,7 @@
         <v>0.04761904761904762</v>
       </c>
       <c r="G377">
-        <v>0.9108491685195835</v>
+        <v>0.9348710317460317</v>
       </c>
     </row>
     <row r="378" spans="1:7">
@@ -21708,7 +21708,7 @@
         <v>-0.1428571428571429</v>
       </c>
       <c r="G378">
-        <v>0.7357648598798121</v>
+        <v>0.7520337301587302</v>
       </c>
     </row>
     <row r="379" spans="1:7">
@@ -21731,7 +21731,7 @@
         <v>-0.4285714285714287</v>
       </c>
       <c r="G379">
-        <v>0.2894032248467901</v>
+        <v>0.2992063492063492</v>
       </c>
     </row>
     <row r="380" spans="1:7">
@@ -21754,7 +21754,7 @@
         <v>-0.8333333333333335</v>
       </c>
       <c r="G380">
-        <v>0.01017554012345672</v>
+        <v>0.01537698412698413</v>
       </c>
     </row>
     <row r="381" spans="1:7">
@@ -21777,7 +21777,7 @@
         <v>0.2142857142857143</v>
       </c>
       <c r="G381">
-        <v>0.6103444156452669</v>
+        <v>0.6190972222222222</v>
       </c>
     </row>
     <row r="382" spans="1:7">
@@ -21800,7 +21800,7 @@
         <v>-0.6190476190476192</v>
       </c>
       <c r="G382">
-        <v>0.1017330374542645</v>
+        <v>0.1149801587301587</v>
       </c>
     </row>
     <row r="383" spans="1:7">
@@ -21823,7 +21823,7 @@
         <v>0.2619047619047619</v>
       </c>
       <c r="G383">
-        <v>0.5309228615658013</v>
+        <v>0.5364087301587301</v>
       </c>
     </row>
     <row r="384" spans="1:7">
@@ -21846,7 +21846,7 @@
         <v>-0.09523809523809525</v>
       </c>
       <c r="G384">
-        <v>0.8225054302036112</v>
+        <v>0.8401289682539682</v>
       </c>
     </row>
     <row r="385" spans="1:7">
@@ -21869,7 +21869,7 @@
         <v>0.2857142857142858</v>
       </c>
       <c r="G385">
-        <v>0.4927262450169571</v>
+        <v>0.5007936507936508</v>
       </c>
     </row>
     <row r="386" spans="1:7">
@@ -21892,7 +21892,7 @@
         <v>-0.4761904761904763</v>
       </c>
       <c r="G386">
-        <v>0.2329355346500979</v>
+        <v>0.2430555555555556</v>
       </c>
     </row>
     <row r="387" spans="1:7">
@@ -21915,7 +21915,7 @@
         <v>0.2619047619047619</v>
       </c>
       <c r="G387">
-        <v>0.5309228615658013</v>
+        <v>0.5364087301587301</v>
       </c>
     </row>
     <row r="388" spans="1:7">
@@ -21938,7 +21938,7 @@
         <v>0.1190476190476191</v>
       </c>
       <c r="G388">
-        <v>0.7788857260523797</v>
+        <v>0.7930059523809524</v>
       </c>
     </row>
     <row r="389" spans="1:7">
@@ -21961,7 +21961,7 @@
         <v>0.1904761904761905</v>
       </c>
       <c r="G389">
-        <v>0.6514014957024816</v>
+        <v>0.6645833333333333</v>
       </c>
     </row>
     <row r="390" spans="1:7">
@@ -21984,7 +21984,7 @@
         <v>-0.04761904761904762</v>
       </c>
       <c r="G390">
-        <v>0.9108491685195835</v>
+        <v>0.9348710317460317</v>
       </c>
     </row>
     <row r="391" spans="1:7">
@@ -22007,7 +22007,7 @@
         <v>-0.2619047619047619</v>
       </c>
       <c r="G391">
-        <v>0.5309228615658013</v>
+        <v>0.5364087301587301</v>
       </c>
     </row>
     <row r="392" spans="1:7">
@@ -22030,7 +22030,7 @@
         <v>-0.6666666666666667</v>
       </c>
       <c r="G392">
-        <v>0.07098765432098751</v>
+        <v>0.08308531746031746</v>
       </c>
     </row>
     <row r="393" spans="1:7">
@@ -22053,7 +22053,7 @@
         <v>0.02380952380952381</v>
       </c>
       <c r="G393">
-        <v>0.9553740118158807</v>
+        <v>0.9767857142857143</v>
       </c>
     </row>
     <row r="394" spans="1:7">
@@ -22076,7 +22076,7 @@
         <v>-0.4761904761904763</v>
       </c>
       <c r="G394">
-        <v>0.2329355346500979</v>
+        <v>0.2430555555555556</v>
       </c>
     </row>
     <row r="395" spans="1:7">
@@ -22099,7 +22099,7 @@
         <v>0.4047619047619048</v>
       </c>
       <c r="G395">
-        <v>0.3198886412288162</v>
+        <v>0.3268353174603175</v>
       </c>
     </row>
     <row r="396" spans="1:7">
@@ -22122,7 +22122,7 @@
         <v>-0.1428571428571429</v>
       </c>
       <c r="G396">
-        <v>0.7357648598798121</v>
+        <v>0.7520337301587302</v>
       </c>
     </row>
     <row r="397" spans="1:7">
@@ -22145,7 +22145,7 @@
         <v>0.2142857142857143</v>
       </c>
       <c r="G397">
-        <v>0.6103444156452669</v>
+        <v>0.6190972222222222</v>
       </c>
     </row>
     <row r="398" spans="1:7">
@@ -22168,7 +22168,7 @@
         <v>-0.4285714285714287</v>
       </c>
       <c r="G398">
-        <v>0.2894032248467901</v>
+        <v>0.2992063492063492</v>
       </c>
     </row>
     <row r="399" spans="1:7">
@@ -22191,7 +22191,7 @@
         <v>0.1904761904761905</v>
       </c>
       <c r="G399">
-        <v>0.6514014957024816</v>
+        <v>0.6645833333333333</v>
       </c>
     </row>
     <row r="400" spans="1:7">
@@ -22214,7 +22214,7 @@
         <v>0.2619047619047619</v>
       </c>
       <c r="G400">
-        <v>0.5309228615658013</v>
+        <v>0.5364087301587301</v>
       </c>
     </row>
     <row r="401" spans="1:7">
@@ -22237,7 +22237,7 @@
         <v>0.04761904761904762</v>
       </c>
       <c r="G401">
-        <v>0.9108491685195835</v>
+        <v>0.9348710317460317</v>
       </c>
     </row>
     <row r="402" spans="1:7">
@@ -22260,7 +22260,7 @@
         <v>-0.1428571428571429</v>
       </c>
       <c r="G402">
-        <v>0.7357648598798121</v>
+        <v>0.7520337301587302</v>
       </c>
     </row>
     <row r="403" spans="1:7">
@@ -22283,7 +22283,7 @@
         <v>-0.4285714285714287</v>
       </c>
       <c r="G403">
-        <v>0.2894032248467901</v>
+        <v>0.2992063492063492</v>
       </c>
     </row>
     <row r="404" spans="1:7">
@@ -22306,7 +22306,7 @@
         <v>-0.8333333333333335</v>
       </c>
       <c r="G404">
-        <v>0.01017554012345672</v>
+        <v>0.01537698412698413</v>
       </c>
     </row>
     <row r="405" spans="1:7">
@@ -22329,7 +22329,7 @@
         <v>0.2142857142857143</v>
       </c>
       <c r="G405">
-        <v>0.6103444156452669</v>
+        <v>0.6190972222222222</v>
       </c>
     </row>
     <row r="406" spans="1:7">
@@ -22352,7 +22352,7 @@
         <v>-0.6190476190476192</v>
       </c>
       <c r="G406">
-        <v>0.1017330374542645</v>
+        <v>0.1149801587301587</v>
       </c>
     </row>
     <row r="407" spans="1:7">
@@ -22375,7 +22375,7 @@
         <v>0.2619047619047619</v>
       </c>
       <c r="G407">
-        <v>0.5309228615658013</v>
+        <v>0.5364087301587301</v>
       </c>
     </row>
     <row r="408" spans="1:7">
@@ -22398,7 +22398,7 @@
         <v>-0.09523809523809525</v>
       </c>
       <c r="G408">
-        <v>0.8225054302036112</v>
+        <v>0.8401289682539682</v>
       </c>
     </row>
     <row r="409" spans="1:7">
@@ -22421,7 +22421,7 @@
         <v>0.2857142857142858</v>
       </c>
       <c r="G409">
-        <v>0.4927262450169571</v>
+        <v>0.5007936507936508</v>
       </c>
     </row>
     <row r="410" spans="1:7">
@@ -22444,7 +22444,7 @@
         <v>0.380952380952381</v>
       </c>
       <c r="G410">
-        <v>0.3518125531175649</v>
+        <v>0.3598710317460317</v>
       </c>
     </row>
     <row r="411" spans="1:7">
@@ -22467,7 +22467,7 @@
         <v>0.380952380952381</v>
       </c>
       <c r="G411">
-        <v>0.3518125531175649</v>
+        <v>0.3598710317460317</v>
       </c>
     </row>
     <row r="412" spans="1:7">
@@ -22490,7 +22490,7 @@
         <v>0.2380952380952381</v>
       </c>
       <c r="G412">
-        <v>0.5701563208157683</v>
+        <v>0.5821428571428572</v>
       </c>
     </row>
     <row r="413" spans="1:7">
@@ -22513,7 +22513,7 @@
         <v>0.6904761904761907</v>
       </c>
       <c r="G413">
-        <v>0.05799031816457269</v>
+        <v>0.06939484126984127</v>
       </c>
     </row>
     <row r="414" spans="1:7">
@@ -22536,7 +22536,7 @@
         <v>0.4761904761904763</v>
       </c>
       <c r="G414">
-        <v>0.2329355346500979</v>
+        <v>0.2430555555555556</v>
       </c>
     </row>
     <row r="415" spans="1:7">
@@ -22559,7 +22559,7 @@
         <v>0.4285714285714287</v>
       </c>
       <c r="G415">
-        <v>0.2894032248467901</v>
+        <v>0.2992063492063492</v>
       </c>
     </row>
     <row r="416" spans="1:7">
@@ -22582,7 +22582,7 @@
         <v>0.5000000000000001</v>
       </c>
       <c r="G416">
-        <v>0.20703125</v>
+        <v>0.2161706349206349</v>
       </c>
     </row>
     <row r="417" spans="1:7">
@@ -22605,7 +22605,7 @@
         <v>-0.380952380952381</v>
       </c>
       <c r="G417">
-        <v>0.3518125531175649</v>
+        <v>0.3598710317460317</v>
       </c>
     </row>
     <row r="418" spans="1:7">
@@ -22628,7 +22628,7 @@
         <v>0.6190476190476192</v>
       </c>
       <c r="G418">
-        <v>0.1017330374542645</v>
+        <v>0.1149801587301587</v>
       </c>
     </row>
     <row r="419" spans="1:7">
@@ -22651,7 +22651,7 @@
         <v>0.1666666666666667</v>
       </c>
       <c r="G419">
-        <v>0.6932388117283947</v>
+        <v>0.7033234126984127</v>
       </c>
     </row>
     <row r="420" spans="1:7">
@@ -22674,7 +22674,7 @@
         <v>-0.5476190476190477</v>
       </c>
       <c r="G420">
-        <v>0.1600256425388963</v>
+        <v>0.1709821428571429</v>
       </c>
     </row>
     <row r="421" spans="1:7">
@@ -22697,7 +22697,7 @@
         <v>0.3571428571428572</v>
       </c>
       <c r="G421">
-        <v>0.3851206435562562</v>
+        <v>0.3893849206349206</v>
       </c>
     </row>
     <row r="422" spans="1:7">
@@ -22720,7 +22720,7 @@
         <v>0.380952380952381</v>
       </c>
       <c r="G422">
-        <v>0.3518125531175649</v>
+        <v>0.3598710317460317</v>
       </c>
     </row>
     <row r="423" spans="1:7">
@@ -22743,7 +22743,7 @@
         <v>0.4047619047619048</v>
       </c>
       <c r="G423">
-        <v>0.3198886412288162</v>
+        <v>0.3268353174603175</v>
       </c>
     </row>
     <row r="424" spans="1:7">
@@ -22766,7 +22766,7 @@
         <v>0.07142857142857144</v>
       </c>
       <c r="G424">
-        <v>0.8665262706759089</v>
+        <v>0.8819940476190476</v>
       </c>
     </row>
     <row r="425" spans="1:7">
@@ -22789,7 +22789,7 @@
         <v>0.5476190476190477</v>
       </c>
       <c r="G425">
-        <v>0.1600256425388963</v>
+        <v>0.1709821428571429</v>
       </c>
     </row>
     <row r="426" spans="1:7">
@@ -22812,7 +22812,7 @@
         <v>0.761904761904762</v>
       </c>
       <c r="G426">
-        <v>0.02800493915307184</v>
+        <v>0.03675595238095238</v>
       </c>
     </row>
     <row r="427" spans="1:7">
@@ -22835,7 +22835,7 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G427">
-        <v>0.07098765432098751</v>
+        <v>0.08308531746031746</v>
       </c>
     </row>
     <row r="428" spans="1:7">
@@ -22858,7 +22858,7 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="G428">
-        <v>0.1827207505397148</v>
+        <v>0.1966269841269841</v>
       </c>
     </row>
     <row r="429" spans="1:7">
@@ -22881,7 +22881,7 @@
         <v>-0.1190476190476191</v>
       </c>
       <c r="G429">
-        <v>0.7788857260523797</v>
+        <v>0.7930059523809524</v>
       </c>
     </row>
     <row r="430" spans="1:7">
@@ -22904,7 +22904,7 @@
         <v>0.6904761904761907</v>
       </c>
       <c r="G430">
-        <v>0.05799031816457269</v>
+        <v>0.06939484126984127</v>
       </c>
     </row>
     <row r="431" spans="1:7">
@@ -22927,7 +22927,7 @@
         <v>0.2380952380952381</v>
       </c>
       <c r="G431">
-        <v>0.5701563208157683</v>
+        <v>0.5821428571428572</v>
       </c>
     </row>
     <row r="432" spans="1:7">
@@ -22950,7 +22950,7 @@
         <v>-0.5000000000000001</v>
       </c>
       <c r="G432">
-        <v>0.20703125</v>
+        <v>0.2161706349206349</v>
       </c>
     </row>
     <row r="433" spans="1:7">
@@ -22973,7 +22973,7 @@
         <v>0.2857142857142858</v>
       </c>
       <c r="G433">
-        <v>0.4927262450169571</v>
+        <v>0.5007936507936508</v>
       </c>
     </row>
     <row r="434" spans="1:7">
@@ -22996,7 +22996,7 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G434">
-        <v>0.07098765432098751</v>
+        <v>0.08308531746031746</v>
       </c>
     </row>
     <row r="435" spans="1:7">
@@ -23019,7 +23019,7 @@
         <v>-0.02380952380952381</v>
       </c>
       <c r="G435">
-        <v>0.9553740118158809</v>
+        <v>0.9767857142857143</v>
       </c>
     </row>
     <row r="436" spans="1:7">
@@ -23042,7 +23042,7 @@
         <v>0.02380952380952381</v>
       </c>
       <c r="G436">
-        <v>0.9553740118158807</v>
+        <v>0.9767857142857143</v>
       </c>
     </row>
     <row r="437" spans="1:7">
@@ -23065,7 +23065,7 @@
         <v>0.1190476190476191</v>
       </c>
       <c r="G437">
-        <v>0.7788857260523797</v>
+        <v>0.7930059523809524</v>
       </c>
     </row>
     <row r="438" spans="1:7">
@@ -23088,7 +23088,7 @@
         <v>0.6190476190476192</v>
       </c>
       <c r="G438">
-        <v>0.1017330374542645</v>
+        <v>0.1149801587301587</v>
       </c>
     </row>
     <row r="439" spans="1:7">
@@ -23111,7 +23111,7 @@
         <v>0.5714285714285715</v>
       </c>
       <c r="G439">
-        <v>0.1389599571607066</v>
+        <v>0.151140873015873</v>
       </c>
     </row>
     <row r="440" spans="1:7">
@@ -23134,7 +23134,7 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="G440">
-        <v>0.1827207505397148</v>
+        <v>0.1966269841269841</v>
       </c>
     </row>
     <row r="441" spans="1:7">
@@ -23157,7 +23157,7 @@
         <v>0.1190476190476191</v>
       </c>
       <c r="G441">
-        <v>0.7788857260523797</v>
+        <v>0.7930059523809524</v>
       </c>
     </row>
     <row r="442" spans="1:7">
@@ -23180,7 +23180,7 @@
         <v>0.7380952380952382</v>
       </c>
       <c r="G442">
-        <v>0.03655276105286075</v>
+        <v>0.04583333333333333</v>
       </c>
     </row>
     <row r="443" spans="1:7">
@@ -23203,7 +23203,7 @@
         <v>-0.2857142857142858</v>
       </c>
       <c r="G443">
-        <v>0.4927262450169571</v>
+        <v>0.5007936507936508</v>
       </c>
     </row>
     <row r="444" spans="1:7">
@@ -23226,7 +23226,7 @@
         <v>-0.1666666666666667</v>
       </c>
       <c r="G444">
-        <v>0.693238811728395</v>
+        <v>0.7033234126984127</v>
       </c>
     </row>
     <row r="445" spans="1:7">
@@ -23249,7 +23249,7 @@
         <v>0.09523809523809525</v>
       </c>
       <c r="G445">
-        <v>0.8225054302036114</v>
+        <v>0.8401289682539682</v>
       </c>
     </row>
     <row r="446" spans="1:7">
@@ -23272,7 +23272,7 @@
         <v>0.2395252523826518</v>
       </c>
       <c r="G446">
-        <v>0.5677721522592927</v>
+        <v>0.5639880952380952</v>
       </c>
     </row>
     <row r="447" spans="1:7">
@@ -23295,7 +23295,7 @@
         <v>0.1916202019061214</v>
       </c>
       <c r="G447">
-        <v>0.649410201122453</v>
+        <v>0.6466269841269842</v>
       </c>
     </row>
     <row r="448" spans="1:7">
@@ -23318,7 +23318,7 @@
         <v>0.03592878785739777</v>
       </c>
       <c r="G448">
-        <v>0.9326914749090883</v>
+        <v>0.9433531746031746</v>
       </c>
     </row>
     <row r="449" spans="1:7">
@@ -23341,7 +23341,7 @@
         <v>0.2395252523826518</v>
       </c>
       <c r="G449">
-        <v>0.5677721522592927</v>
+        <v>0.5639880952380952</v>
       </c>
     </row>
     <row r="450" spans="1:7">
@@ -23364,7 +23364,7 @@
         <v>0.4071929290505081</v>
       </c>
       <c r="G450">
-        <v>0.3167091849161282</v>
+        <v>0.3145833333333333</v>
       </c>
     </row>
     <row r="451" spans="1:7">
@@ -23387,7 +23387,7 @@
         <v>0.203596464525254</v>
       </c>
       <c r="G451">
-        <v>0.6286746732890389</v>
+        <v>0.6293650793650793</v>
       </c>
     </row>
     <row r="452" spans="1:7">
@@ -23410,7 +23410,7 @@
         <v>-0.5509080804800992</v>
       </c>
       <c r="G452">
-        <v>0.157018421997891</v>
+        <v>0.1626984126984127</v>
       </c>
     </row>
     <row r="453" spans="1:7">
@@ -23433,7 +23433,7 @@
         <v>0.5149792926227015</v>
       </c>
       <c r="G453">
-        <v>0.1915493134158658</v>
+        <v>0.197718253968254</v>
       </c>
     </row>
     <row r="454" spans="1:7">
@@ -23456,7 +23456,7 @@
         <v>0.03592878785739777</v>
       </c>
       <c r="G454">
-        <v>0.9326914749090883</v>
+        <v>0.9433531746031746</v>
       </c>
     </row>
     <row r="455" spans="1:7">
@@ -23479,7 +23479,7 @@
         <v>0.08383383833392813</v>
       </c>
       <c r="G455">
-        <v>0.8435464923328301</v>
+        <v>0.8493055555555555</v>
       </c>
     </row>
     <row r="456" spans="1:7">
@@ -23502,7 +23502,7 @@
         <v>-0.2874303028591821</v>
       </c>
       <c r="G456">
-        <v>0.4900154852220339</v>
+        <v>0.4844246031746032</v>
       </c>
     </row>
     <row r="457" spans="1:7">
@@ -23525,7 +23525,7 @@
         <v>0.1916202019061214</v>
       </c>
       <c r="G457">
-        <v>0.649410201122453</v>
+        <v>0.6466269841269842</v>
       </c>
     </row>
     <row r="458" spans="1:7">
@@ -23548,7 +23548,7 @@
         <v>-0.4096682888050979</v>
       </c>
       <c r="G458">
-        <v>0.313487214282711</v>
+        <v>0.3126984126984127</v>
       </c>
     </row>
     <row r="459" spans="1:7">
@@ -23571,7 +23571,7 @@
         <v>-0.433766423440692</v>
       </c>
       <c r="G459">
-        <v>0.2829476709180395</v>
+        <v>0.283531746031746</v>
       </c>
     </row>
     <row r="460" spans="1:7">
@@ -23594,7 +23594,7 @@
         <v>-0.07229440390678199</v>
       </c>
       <c r="G460">
-        <v>0.8649195587700262</v>
+        <v>0.8698412698412699</v>
       </c>
     </row>
     <row r="461" spans="1:7">
@@ -23617,7 +23617,7 @@
         <v>-0.6626987024788349</v>
       </c>
       <c r="G461">
-        <v>0.07330582330837648</v>
+        <v>0.08214285714285714</v>
       </c>
     </row>
     <row r="462" spans="1:7">
@@ -23640,7 +23640,7 @@
         <v>0.04819626927118799</v>
       </c>
       <c r="G462">
-        <v>0.909771840305317</v>
+        <v>0.9198412698412698</v>
       </c>
     </row>
     <row r="463" spans="1:7">
@@ -23663,7 +23663,7 @@
         <v>-0.180736009766955</v>
       </c>
       <c r="G463">
-        <v>0.6684274536427575</v>
+        <v>0.6694444444444444</v>
       </c>
     </row>
     <row r="464" spans="1:7">
@@ -23686,7 +23686,7 @@
         <v>0.289177615627128</v>
       </c>
       <c r="G464">
-        <v>0.4872612723244323</v>
+        <v>0.4845238095238095</v>
       </c>
     </row>
     <row r="465" spans="1:7">
@@ -23709,7 +23709,7 @@
         <v>-0.4096682888050979</v>
       </c>
       <c r="G465">
-        <v>0.313487214282711</v>
+        <v>0.3126984126984127</v>
       </c>
     </row>
     <row r="466" spans="1:7">
@@ -23732,7 +23732,7 @@
         <v>-0.012049067317797</v>
       </c>
       <c r="G466">
-        <v>0.9774101852887365</v>
+        <v>0.9880952380952381</v>
       </c>
     </row>
     <row r="467" spans="1:7">
@@ -23755,7 +23755,7 @@
         <v>-0.132539740495767</v>
       </c>
       <c r="G467">
-        <v>0.754383019857472</v>
+        <v>0.756547619047619</v>
       </c>
     </row>
     <row r="468" spans="1:7">
@@ -23778,7 +23778,7 @@
         <v>0.6626987024788349</v>
       </c>
       <c r="G468">
-        <v>0.07330582330837648</v>
+        <v>0.08214285714285714</v>
       </c>
     </row>
     <row r="469" spans="1:7">
@@ -23801,7 +23801,7 @@
         <v>-0.132539740495767</v>
       </c>
       <c r="G469">
-        <v>0.754383019857472</v>
+        <v>0.756547619047619</v>
       </c>
     </row>
     <row r="470" spans="1:7">
@@ -23824,7 +23824,7 @@
         <v>-0.1190476190476191</v>
       </c>
       <c r="G470">
-        <v>0.7788857260523797</v>
+        <v>0.7930059523809524</v>
       </c>
     </row>
     <row r="471" spans="1:7">
@@ -23847,7 +23847,7 @@
         <v>-0.2380952380952381</v>
       </c>
       <c r="G471">
-        <v>0.5701563208157683</v>
+        <v>0.5821428571428572</v>
       </c>
     </row>
     <row r="472" spans="1:7">
@@ -23870,7 +23870,7 @@
         <v>-0.3095238095238096</v>
       </c>
       <c r="G472">
-        <v>0.4556448907375821</v>
+        <v>0.4618055555555556</v>
       </c>
     </row>
     <row r="473" spans="1:7">
@@ -23893,7 +23893,7 @@
         <v>-0.4523809523809525</v>
       </c>
       <c r="G473">
-        <v>0.2604047674368849</v>
+        <v>0.2674603174603175</v>
       </c>
     </row>
     <row r="474" spans="1:7">
@@ -23916,7 +23916,7 @@
         <v>0.3571428571428572</v>
       </c>
       <c r="G474">
-        <v>0.3851206435562562</v>
+        <v>0.3893849206349206</v>
       </c>
     </row>
     <row r="475" spans="1:7">
@@ -23939,7 +23939,7 @@
         <v>0.1666666666666667</v>
       </c>
       <c r="G475">
-        <v>0.6932388117283947</v>
+        <v>0.7033234126984127</v>
       </c>
     </row>
     <row r="476" spans="1:7">
@@ -23962,7 +23962,7 @@
         <v>-0.3333333333333334</v>
       </c>
       <c r="G476">
-        <v>0.4197530864197531</v>
+        <v>0.4278769841269841</v>
       </c>
     </row>
     <row r="477" spans="1:7">
@@ -23985,7 +23985,7 @@
         <v>0.4047619047619048</v>
       </c>
       <c r="G477">
-        <v>0.3198886412288162</v>
+        <v>0.3268353174603175</v>
       </c>
     </row>
     <row r="478" spans="1:7">
@@ -24008,7 +24008,7 @@
         <v>-0.04761904761904762</v>
       </c>
       <c r="G478">
-        <v>0.9108491685195835</v>
+        <v>0.9348710317460317</v>
       </c>
     </row>
     <row r="479" spans="1:7">
@@ -24031,7 +24031,7 @@
         <v>-0.07142857142857144</v>
       </c>
       <c r="G479">
-        <v>0.8665262706759089</v>
+        <v>0.8819940476190476</v>
       </c>
     </row>
     <row r="480" spans="1:7">
@@ -24054,7 +24054,7 @@
         <v>0.3571428571428572</v>
       </c>
       <c r="G480">
-        <v>0.3851206435562562</v>
+        <v>0.3893849206349206</v>
       </c>
     </row>
     <row r="481" spans="1:7">
@@ -24077,7 +24077,7 @@
         <v>-0.1904761904761905</v>
       </c>
       <c r="G481">
-        <v>0.6514014957024816</v>
+        <v>0.6645833333333333</v>
       </c>
     </row>
     <row r="482" spans="1:7">
@@ -24100,7 +24100,7 @@
         <v>0.1666666666666667</v>
       </c>
       <c r="G482">
-        <v>0.6932388117283947</v>
+        <v>0.7033234126984127</v>
       </c>
     </row>
     <row r="483" spans="1:7">
@@ -24123,7 +24123,7 @@
         <v>0.4761904761904763</v>
       </c>
       <c r="G483">
-        <v>0.2329355346500979</v>
+        <v>0.2430555555555556</v>
       </c>
     </row>
     <row r="484" spans="1:7">
@@ -24146,7 +24146,7 @@
         <v>-0.2380952380952381</v>
       </c>
       <c r="G484">
-        <v>0.5701563208157683</v>
+        <v>0.5821428571428572</v>
       </c>
     </row>
     <row r="485" spans="1:7">
@@ -24169,7 +24169,7 @@
         <v>0.3571428571428572</v>
       </c>
       <c r="G485">
-        <v>0.3851206435562562</v>
+        <v>0.3893849206349206</v>
       </c>
     </row>
     <row r="486" spans="1:7">
@@ -24192,7 +24192,7 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G486">
-        <v>0.4197530864197531</v>
+        <v>0.4278769841269841</v>
       </c>
     </row>
     <row r="487" spans="1:7">
@@ -24215,7 +24215,7 @@
         <v>0.4047619047619048</v>
       </c>
       <c r="G487">
-        <v>0.3198886412288162</v>
+        <v>0.3268353174603175</v>
       </c>
     </row>
     <row r="488" spans="1:7">
@@ -24238,7 +24238,7 @@
         <v>0.380952380952381</v>
       </c>
       <c r="G488">
-        <v>0.3518125531175649</v>
+        <v>0.3598710317460317</v>
       </c>
     </row>
     <row r="489" spans="1:7">
@@ -24261,7 +24261,7 @@
         <v>0.2380952380952381</v>
       </c>
       <c r="G489">
-        <v>0.5701563208157683</v>
+        <v>0.5821428571428572</v>
       </c>
     </row>
     <row r="490" spans="1:7">
@@ -24284,7 +24284,7 @@
         <v>0.1904761904761905</v>
       </c>
       <c r="G490">
-        <v>0.6514014957024816</v>
+        <v>0.6645833333333333</v>
       </c>
     </row>
     <row r="491" spans="1:7">
@@ -24307,7 +24307,7 @@
         <v>-0.2142857142857143</v>
       </c>
       <c r="G491">
-        <v>0.6103444156452666</v>
+        <v>0.6190972222222222</v>
       </c>
     </row>
     <row r="492" spans="1:7">
@@ -24330,7 +24330,7 @@
         <v>-0.6190476190476192</v>
       </c>
       <c r="G492">
-        <v>0.1017330374542645</v>
+        <v>0.1149801587301587</v>
       </c>
     </row>
     <row r="493" spans="1:7">
@@ -24353,7 +24353,7 @@
         <v>-0.3333333333333334</v>
       </c>
       <c r="G493">
-        <v>0.4197530864197531</v>
+        <v>0.4278769841269841</v>
       </c>
     </row>
     <row r="494" spans="1:7">
@@ -24376,7 +24376,7 @@
         <v>-0.3095238095238096</v>
       </c>
       <c r="G494">
-        <v>0.4556448907375821</v>
+        <v>0.4618055555555556</v>
       </c>
     </row>
     <row r="495" spans="1:7">
@@ -24399,7 +24399,7 @@
         <v>0.380952380952381</v>
       </c>
       <c r="G495">
-        <v>0.3518125531175649</v>
+        <v>0.3598710317460317</v>
       </c>
     </row>
     <row r="496" spans="1:7">
@@ -24422,7 +24422,7 @@
         <v>-0.3333333333333334</v>
       </c>
       <c r="G496">
-        <v>0.4197530864197531</v>
+        <v>0.4278769841269841</v>
       </c>
     </row>
     <row r="497" spans="1:7">
@@ -24445,7 +24445,7 @@
         <v>-0.1190476190476191</v>
       </c>
       <c r="G497">
-        <v>0.7788857260523797</v>
+        <v>0.7930059523809524</v>
       </c>
     </row>
     <row r="498" spans="1:7">
@@ -24468,7 +24468,7 @@
         <v>0.6190476190476192</v>
       </c>
       <c r="G498">
-        <v>0.1017330374542645</v>
+        <v>0.1149801587301587</v>
       </c>
     </row>
     <row r="499" spans="1:7">
@@ -24491,7 +24491,7 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G499">
-        <v>0.4197530864197531</v>
+        <v>0.4278769841269841</v>
       </c>
     </row>
     <row r="500" spans="1:7">
@@ -24514,7 +24514,7 @@
         <v>0.02380952380952381</v>
       </c>
       <c r="G500">
-        <v>0.9553740118158807</v>
+        <v>0.9767857142857143</v>
       </c>
     </row>
     <row r="501" spans="1:7">
@@ -24537,7 +24537,7 @@
         <v>0.4761904761904763</v>
       </c>
       <c r="G501">
-        <v>0.2329355346500979</v>
+        <v>0.2430555555555556</v>
       </c>
     </row>
     <row r="502" spans="1:7">
@@ -24560,7 +24560,7 @@
         <v>-0.1904761904761905</v>
       </c>
       <c r="G502">
-        <v>0.6514014957024816</v>
+        <v>0.6645833333333333</v>
       </c>
     </row>
     <row r="503" spans="1:7">
@@ -24583,7 +24583,7 @@
         <v>0.1666666666666667</v>
       </c>
       <c r="G503">
-        <v>0.6932388117283947</v>
+        <v>0.7033234126984127</v>
       </c>
     </row>
     <row r="504" spans="1:7">
@@ -24606,7 +24606,7 @@
         <v>-0.2380952380952381</v>
       </c>
       <c r="G504">
-        <v>0.5701563208157683</v>
+        <v>0.5821428571428572</v>
       </c>
     </row>
     <row r="505" spans="1:7">
@@ -24629,7 +24629,7 @@
         <v>-0.4523809523809525</v>
       </c>
       <c r="G505">
-        <v>0.2604047674368849</v>
+        <v>0.2674603174603175</v>
       </c>
     </row>
     <row r="506" spans="1:7">
@@ -24652,7 +24652,7 @@
         <v>-0.2857142857142858</v>
       </c>
       <c r="G506">
-        <v>0.4927262450169571</v>
+        <v>0.5007936507936508</v>
       </c>
     </row>
     <row r="507" spans="1:7">
@@ -24675,7 +24675,7 @@
         <v>0.3571428571428572</v>
       </c>
       <c r="G507">
-        <v>0.3851206435562562</v>
+        <v>0.3893849206349206</v>
       </c>
     </row>
     <row r="508" spans="1:7">
@@ -24698,7 +24698,7 @@
         <v>-0.2619047619047619</v>
       </c>
       <c r="G508">
-        <v>0.5309228615658013</v>
+        <v>0.5364087301587301</v>
       </c>
     </row>
     <row r="509" spans="1:7">
@@ -24721,7 +24721,7 @@
         <v>-0.2142857142857143</v>
       </c>
       <c r="G509">
-        <v>0.6103444156452666</v>
+        <v>0.6190972222222222</v>
       </c>
     </row>
     <row r="510" spans="1:7">
@@ -24744,7 +24744,7 @@
         <v>0.4523809523809525</v>
       </c>
       <c r="G510">
-        <v>0.2604047674368849</v>
+        <v>0.2674603174603175</v>
       </c>
     </row>
     <row r="511" spans="1:7">
@@ -24767,7 +24767,7 @@
         <v>0.1904761904761905</v>
       </c>
       <c r="G511">
-        <v>0.6514014957024816</v>
+        <v>0.6645833333333333</v>
       </c>
     </row>
     <row r="512" spans="1:7">
@@ -24790,7 +24790,7 @@
         <v>-0.07142857142857144</v>
       </c>
       <c r="G512">
-        <v>0.8665262706759089</v>
+        <v>0.8819940476190476</v>
       </c>
     </row>
     <row r="513" spans="1:7">
@@ -24813,7 +24813,7 @@
         <v>0.5952380952380953</v>
       </c>
       <c r="G513">
-        <v>0.1195298061387926</v>
+        <v>0.1322916666666667</v>
       </c>
     </row>
     <row r="514" spans="1:7">
@@ -24836,7 +24836,7 @@
         <v>-0.2857142857142858</v>
       </c>
       <c r="G514">
-        <v>0.4927262450169571</v>
+        <v>0.5007936507936508</v>
       </c>
     </row>
     <row r="515" spans="1:7">
@@ -24859,7 +24859,7 @@
         <v>0.04761904761904762</v>
       </c>
       <c r="G515">
-        <v>0.9108491685195835</v>
+        <v>0.9348710317460317</v>
       </c>
     </row>
     <row r="516" spans="1:7">
@@ -24882,7 +24882,7 @@
         <v>-0.1428571428571429</v>
       </c>
       <c r="G516">
-        <v>0.7357648598798121</v>
+        <v>0.7520337301587302</v>
       </c>
     </row>
     <row r="517" spans="1:7">
@@ -24905,7 +24905,7 @@
         <v>-0.4285714285714287</v>
       </c>
       <c r="G517">
-        <v>0.2894032248467901</v>
+        <v>0.2992063492063492</v>
       </c>
     </row>
     <row r="518" spans="1:7">
@@ -24928,7 +24928,7 @@
         <v>-0.3095238095238096</v>
       </c>
       <c r="G518">
-        <v>0.4556448907375821</v>
+        <v>0.4618055555555556</v>
       </c>
     </row>
     <row r="519" spans="1:7">
@@ -24951,7 +24951,7 @@
         <v>0.380952380952381</v>
       </c>
       <c r="G519">
-        <v>0.3518125531175649</v>
+        <v>0.3598710317460317</v>
       </c>
     </row>
     <row r="520" spans="1:7">
@@ -24974,7 +24974,7 @@
         <v>-0.3333333333333334</v>
       </c>
       <c r="G520">
-        <v>0.4197530864197531</v>
+        <v>0.4278769841269841</v>
       </c>
     </row>
     <row r="521" spans="1:7">
@@ -24997,7 +24997,7 @@
         <v>-0.1190476190476191</v>
       </c>
       <c r="G521">
-        <v>0.7788857260523797</v>
+        <v>0.7930059523809524</v>
       </c>
     </row>
     <row r="522" spans="1:7">
@@ -25020,7 +25020,7 @@
         <v>0.6190476190476192</v>
       </c>
       <c r="G522">
-        <v>0.1017330374542645</v>
+        <v>0.1149801587301587</v>
       </c>
     </row>
     <row r="523" spans="1:7">
@@ -25043,7 +25043,7 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G523">
-        <v>0.4197530864197531</v>
+        <v>0.4278769841269841</v>
       </c>
     </row>
     <row r="524" spans="1:7">
@@ -25066,7 +25066,7 @@
         <v>0.02380952380952381</v>
       </c>
       <c r="G524">
-        <v>0.9553740118158807</v>
+        <v>0.9767857142857143</v>
       </c>
     </row>
     <row r="525" spans="1:7">
@@ -25089,7 +25089,7 @@
         <v>0.4761904761904763</v>
       </c>
       <c r="G525">
-        <v>0.2329355346500979</v>
+        <v>0.2430555555555556</v>
       </c>
     </row>
     <row r="526" spans="1:7">
@@ -25112,7 +25112,7 @@
         <v>-0.1904761904761905</v>
       </c>
       <c r="G526">
-        <v>0.6514014957024816</v>
+        <v>0.6645833333333333</v>
       </c>
     </row>
     <row r="527" spans="1:7">
@@ -25135,7 +25135,7 @@
         <v>0.1666666666666667</v>
       </c>
       <c r="G527">
-        <v>0.6932388117283947</v>
+        <v>0.7033234126984127</v>
       </c>
     </row>
     <row r="528" spans="1:7">
@@ -25158,7 +25158,7 @@
         <v>-0.2380952380952381</v>
       </c>
       <c r="G528">
-        <v>0.5701563208157683</v>
+        <v>0.5821428571428572</v>
       </c>
     </row>
     <row r="529" spans="1:7">
@@ -25181,7 +25181,7 @@
         <v>-0.4523809523809525</v>
       </c>
       <c r="G529">
-        <v>0.2604047674368849</v>
+        <v>0.2674603174603175</v>
       </c>
     </row>
     <row r="530" spans="1:7">
@@ -25204,7 +25204,7 @@
         <v>0.02380952380952381</v>
       </c>
       <c r="G530">
-        <v>0.9553740118158807</v>
+        <v>0.9767857142857143</v>
       </c>
     </row>
     <row r="531" spans="1:7">
@@ -25227,7 +25227,7 @@
         <v>0.2380952380952381</v>
       </c>
       <c r="G531">
-        <v>0.5701563208157683</v>
+        <v>0.5821428571428572</v>
       </c>
     </row>
     <row r="532" spans="1:7">
@@ -25250,7 +25250,7 @@
         <v>-0.1428571428571429</v>
       </c>
       <c r="G532">
-        <v>0.7357648598798121</v>
+        <v>0.7520337301587302</v>
       </c>
     </row>
     <row r="533" spans="1:7">
@@ -25273,7 +25273,7 @@
         <v>-0.2857142857142858</v>
       </c>
       <c r="G533">
-        <v>0.4927262450169571</v>
+        <v>0.5007936507936508</v>
       </c>
     </row>
     <row r="534" spans="1:7">
@@ -25296,7 +25296,7 @@
         <v>-0.4047619047619048</v>
       </c>
       <c r="G534">
-        <v>0.3198886412288163</v>
+        <v>0.3268353174603175</v>
       </c>
     </row>
     <row r="535" spans="1:7">
@@ -25319,7 +25319,7 @@
         <v>-0.1190476190476191</v>
       </c>
       <c r="G535">
-        <v>0.7788857260523797</v>
+        <v>0.7930059523809524</v>
       </c>
     </row>
     <row r="536" spans="1:7">
@@ -25342,7 +25342,7 @@
         <v>0.02380952380952381</v>
       </c>
       <c r="G536">
-        <v>0.9553740118158807</v>
+        <v>0.9767857142857143</v>
       </c>
     </row>
     <row r="537" spans="1:7">
@@ -25365,7 +25365,7 @@
         <v>-0.07142857142857144</v>
       </c>
       <c r="G537">
-        <v>0.8665262706759089</v>
+        <v>0.8819940476190476</v>
       </c>
     </row>
     <row r="538" spans="1:7">
@@ -25388,7 +25388,7 @@
         <v>0.1428571428571429</v>
       </c>
       <c r="G538">
-        <v>0.7357648598798119</v>
+        <v>0.7520337301587302</v>
       </c>
     </row>
     <row r="539" spans="1:7">
@@ -25411,7 +25411,7 @@
         <v>-0.1428571428571429</v>
       </c>
       <c r="G539">
-        <v>0.7357648598798121</v>
+        <v>0.7520337301587302</v>
       </c>
     </row>
     <row r="540" spans="1:7">
@@ -25434,7 +25434,7 @@
         <v>0.4523809523809525</v>
       </c>
       <c r="G540">
-        <v>0.2604047674368849</v>
+        <v>0.2674603174603175</v>
       </c>
     </row>
     <row r="541" spans="1:7">
@@ -25457,7 +25457,7 @@
         <v>-0.3333333333333334</v>
       </c>
       <c r="G541">
-        <v>0.4197530864197531</v>
+        <v>0.4278769841269841</v>
       </c>
     </row>
     <row r="542" spans="1:7">
@@ -25480,7 +25480,7 @@
         <v>0.2619047619047619</v>
       </c>
       <c r="G542">
-        <v>0.5309228615658013</v>
+        <v>0.5364087301587301</v>
       </c>
     </row>
     <row r="543" spans="1:7">
@@ -25503,7 +25503,7 @@
         <v>-0.04761904761904762</v>
       </c>
       <c r="G543">
-        <v>0.9108491685195835</v>
+        <v>0.9348710317460317</v>
       </c>
     </row>
     <row r="544" spans="1:7">
@@ -25549,7 +25549,7 @@
         <v>-0.1428571428571429</v>
       </c>
       <c r="G545">
-        <v>0.7357648598798121</v>
+        <v>0.7520337301587302</v>
       </c>
     </row>
     <row r="546" spans="1:7">
@@ -25572,7 +25572,7 @@
         <v>-0.6190476190476192</v>
       </c>
       <c r="G546">
-        <v>0.1017330374542645</v>
+        <v>0.1149801587301587</v>
       </c>
     </row>
     <row r="547" spans="1:7">
@@ -25595,7 +25595,7 @@
         <v>-0.3095238095238096</v>
       </c>
       <c r="G547">
-        <v>0.4556448907375821</v>
+        <v>0.4618055555555556</v>
       </c>
     </row>
     <row r="548" spans="1:7">
@@ -25618,7 +25618,7 @@
         <v>0.380952380952381</v>
       </c>
       <c r="G548">
-        <v>0.3518125531175649</v>
+        <v>0.3598710317460317</v>
       </c>
     </row>
     <row r="549" spans="1:7">
@@ -25641,7 +25641,7 @@
         <v>-0.2380952380952381</v>
       </c>
       <c r="G549">
-        <v>0.5701563208157683</v>
+        <v>0.5821428571428572</v>
       </c>
     </row>
     <row r="550" spans="1:7">
@@ -25664,7 +25664,7 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G550">
-        <v>0.4197530864197531</v>
+        <v>0.4278769841269841</v>
       </c>
     </row>
     <row r="551" spans="1:7">
@@ -25687,7 +25687,7 @@
         <v>-0.4761904761904763</v>
       </c>
       <c r="G551">
-        <v>0.2329355346500979</v>
+        <v>0.2430555555555556</v>
       </c>
     </row>
     <row r="552" spans="1:7">
@@ -25710,7 +25710,7 @@
         <v>0.3095238095238096</v>
       </c>
       <c r="G552">
-        <v>0.4556448907375821</v>
+        <v>0.4618055555555556</v>
       </c>
     </row>
     <row r="553" spans="1:7">
@@ -25733,7 +25733,7 @@
         <v>0.02380952380952381</v>
       </c>
       <c r="G553">
-        <v>0.9553740118158807</v>
+        <v>0.9767857142857143</v>
       </c>
     </row>
     <row r="554" spans="1:7">
@@ -25756,7 +25756,7 @@
         <v>0.3571428571428572</v>
       </c>
       <c r="G554">
-        <v>0.3851206435562562</v>
+        <v>0.3893849206349206</v>
       </c>
     </row>
     <row r="555" spans="1:7">
@@ -25779,7 +25779,7 @@
         <v>-0.04761904761904762</v>
       </c>
       <c r="G555">
-        <v>0.9108491685195835</v>
+        <v>0.9348710317460317</v>
       </c>
     </row>
     <row r="556" spans="1:7">
@@ -25802,7 +25802,7 @@
         <v>0.1904761904761905</v>
       </c>
       <c r="G556">
-        <v>0.6514014957024816</v>
+        <v>0.6645833333333333</v>
       </c>
     </row>
     <row r="557" spans="1:7">
@@ -25825,7 +25825,7 @@
         <v>0.1904761904761905</v>
       </c>
       <c r="G557">
-        <v>0.6514014957024816</v>
+        <v>0.6645833333333333</v>
       </c>
     </row>
     <row r="558" spans="1:7">
@@ -25848,7 +25848,7 @@
         <v>-0.6190476190476192</v>
       </c>
       <c r="G558">
-        <v>0.1017330374542645</v>
+        <v>0.1149801587301587</v>
       </c>
     </row>
     <row r="559" spans="1:7">
@@ -25871,7 +25871,7 @@
         <v>-0.2142857142857143</v>
       </c>
       <c r="G559">
-        <v>0.6103444156452666</v>
+        <v>0.6190972222222222</v>
       </c>
     </row>
     <row r="560" spans="1:7">
@@ -25894,7 +25894,7 @@
         <v>0.4761904761904763</v>
       </c>
       <c r="G560">
-        <v>0.2329355346500979</v>
+        <v>0.2430555555555556</v>
       </c>
     </row>
     <row r="561" spans="1:7">
@@ -25917,7 +25917,7 @@
         <v>-0.6190476190476192</v>
       </c>
       <c r="G561">
-        <v>0.1017330374542645</v>
+        <v>0.1149801587301587</v>
       </c>
     </row>
     <row r="562" spans="1:7">
@@ -25940,7 +25940,7 @@
         <v>0.4285714285714287</v>
       </c>
       <c r="G562">
-        <v>0.2894032248467901</v>
+        <v>0.2992063492063492</v>
       </c>
     </row>
     <row r="563" spans="1:7">
@@ -25963,7 +25963,7 @@
         <v>-0.3333333333333334</v>
       </c>
       <c r="G563">
-        <v>0.4197530864197531</v>
+        <v>0.4278769841269841</v>
       </c>
     </row>
     <row r="564" spans="1:7">
@@ -25986,7 +25986,7 @@
         <v>0.07142857142857144</v>
       </c>
       <c r="G564">
-        <v>0.8665262706759089</v>
+        <v>0.8819940476190476</v>
       </c>
     </row>
     <row r="565" spans="1:7">
@@ -26009,7 +26009,7 @@
         <v>0.1666666666666667</v>
       </c>
       <c r="G565">
-        <v>0.6932388117283947</v>
+        <v>0.7033234126984127</v>
       </c>
     </row>
     <row r="566" spans="1:7">
@@ -26032,7 +26032,7 @@
         <v>-0.2754540402400496</v>
       </c>
       <c r="G566">
-        <v>0.5090540726550731</v>
+        <v>0.5052579365079365</v>
       </c>
     </row>
     <row r="567" spans="1:7">
@@ -26055,7 +26055,7 @@
         <v>0.3712641411931104</v>
       </c>
       <c r="G567">
-        <v>0.365202058019778</v>
+        <v>0.3626984126984127</v>
       </c>
     </row>
     <row r="568" spans="1:7">
@@ -26078,7 +26078,7 @@
         <v>0.08383383833392813</v>
       </c>
       <c r="G568">
-        <v>0.8435464923328301</v>
+        <v>0.8493055555555555</v>
       </c>
     </row>
     <row r="569" spans="1:7">
@@ -26101,7 +26101,7 @@
         <v>-0.1916202019061214</v>
       </c>
       <c r="G569">
-        <v>0.649410201122453</v>
+        <v>0.6466269841269842</v>
       </c>
     </row>
     <row r="570" spans="1:7">
@@ -26124,7 +26124,7 @@
         <v>0.02395252523826518</v>
       </c>
       <c r="G570">
-        <v>0.9551061898789129</v>
+        <v>0.9642857142857143</v>
       </c>
     </row>
     <row r="571" spans="1:7">
@@ -26147,7 +26147,7 @@
         <v>-0.09581010095306072</v>
       </c>
       <c r="G571">
-        <v>0.8214524032504529</v>
+        <v>0.8247023809523809</v>
       </c>
     </row>
     <row r="572" spans="1:7">
@@ -26170,7 +26170,7 @@
         <v>0.467074242146171</v>
       </c>
       <c r="G572">
-        <v>0.2432699166339955</v>
+        <v>0.2464285714285714</v>
       </c>
     </row>
     <row r="573" spans="1:7">
@@ -26193,7 +26193,7 @@
         <v>-0.09581010095306072</v>
       </c>
       <c r="G573">
-        <v>0.8214524032504529</v>
+        <v>0.8247023809523809</v>
       </c>
     </row>
     <row r="574" spans="1:7">
@@ -26216,7 +26216,7 @@
         <v>-0.1197626261913259</v>
       </c>
       <c r="G574">
-        <v>0.7775830437712572</v>
+        <v>0.779265873015873</v>
       </c>
     </row>
     <row r="575" spans="1:7">
@@ -26239,7 +26239,7 @@
         <v>-0.01197626261913259</v>
       </c>
       <c r="G575">
-        <v>0.977546654703887</v>
+        <v>0.9904761904761905</v>
       </c>
     </row>
     <row r="576" spans="1:7">
@@ -26262,7 +26262,7 @@
         <v>-0.07185757571479554</v>
       </c>
       <c r="G576">
-        <v>0.8657301238340009</v>
+        <v>0.8723214285714286</v>
       </c>
     </row>
     <row r="577" spans="1:7">
@@ -26285,7 +26285,7 @@
         <v>-0.3353353533357125</v>
       </c>
       <c r="G577">
-        <v>0.4167915909642739</v>
+        <v>0.4104166666666667</v>
       </c>
     </row>
     <row r="578" spans="1:7">
@@ -26308,7 +26308,7 @@
         <v>0.879581914199181</v>
       </c>
       <c r="G578">
-        <v>0.003980558879022643</v>
+        <v>0.006349206349206349</v>
       </c>
     </row>
     <row r="579" spans="1:7">
@@ -26331,7 +26331,7 @@
         <v>-0.03614720195339099</v>
       </c>
       <c r="G579">
-        <v>0.9322830115259055</v>
+        <v>0.9416666666666667</v>
       </c>
     </row>
     <row r="580" spans="1:7">
@@ -26354,7 +26354,7 @@
         <v>-0.156637875131361</v>
       </c>
       <c r="G580">
-        <v>0.7110725947268531</v>
+        <v>0.7109126984126984</v>
       </c>
     </row>
     <row r="581" spans="1:7">
@@ -26377,7 +26377,7 @@
         <v>0.879581914199181</v>
       </c>
       <c r="G581">
-        <v>0.003980558879022643</v>
+        <v>0.006349206349206349</v>
       </c>
     </row>
     <row r="582" spans="1:7">
@@ -26400,7 +26400,7 @@
         <v>0.012049067317797</v>
       </c>
       <c r="G582">
-        <v>0.9774101852887365</v>
+        <v>0.9880952380952381</v>
       </c>
     </row>
     <row r="583" spans="1:7">
@@ -26423,7 +26423,7 @@
         <v>0.421717356122895</v>
       </c>
       <c r="G583">
-        <v>0.2980286979370499</v>
+        <v>0.2966269841269841</v>
       </c>
     </row>
     <row r="584" spans="1:7">
@@ -26446,7 +26446,7 @@
         <v>-0.03614720195339099</v>
       </c>
       <c r="G584">
-        <v>0.9322830115259055</v>
+        <v>0.9416666666666667</v>
       </c>
     </row>
     <row r="585" spans="1:7">
@@ -26469,7 +26469,7 @@
         <v>0.373521086851707</v>
       </c>
       <c r="G585">
-        <v>0.3620625982631651</v>
+        <v>0.3615079365079365</v>
       </c>
     </row>
     <row r="586" spans="1:7">
@@ -26492,7 +26492,7 @@
         <v>0.48196269271188</v>
       </c>
       <c r="G586">
-        <v>0.2265105557960854</v>
+        <v>0.2325396825396825</v>
       </c>
     </row>
     <row r="587" spans="1:7">
@@ -26515,7 +26515,7 @@
         <v>-0.60245336588985</v>
       </c>
       <c r="G587">
-        <v>0.1139644808451555</v>
+        <v>0.1228174603174603</v>
       </c>
     </row>
     <row r="588" spans="1:7">
@@ -26538,7 +26538,7 @@
         <v>-0.8072875102923989</v>
       </c>
       <c r="G588">
-        <v>0.01540604211410598</v>
+        <v>0.02083333333333333</v>
       </c>
     </row>
     <row r="589" spans="1:7">
@@ -26561,7 +26561,7 @@
         <v>0.301226682944925</v>
       </c>
       <c r="G589">
-        <v>0.468435636896902</v>
+        <v>0.4619047619047619</v>
       </c>
     </row>
     <row r="590" spans="1:7">
@@ -26584,7 +26584,7 @@
         <v>0.3571428571428572</v>
       </c>
       <c r="G590">
-        <v>0.3851206435562562</v>
+        <v>0.3893849206349206</v>
       </c>
     </row>
     <row r="591" spans="1:7">
@@ -26607,7 +26607,7 @@
         <v>-0.02380952380952381</v>
       </c>
       <c r="G591">
-        <v>0.9553740118158809</v>
+        <v>0.9767857142857143</v>
       </c>
     </row>
     <row r="592" spans="1:7">
@@ -26630,7 +26630,7 @@
         <v>0.2380952380952381</v>
       </c>
       <c r="G592">
-        <v>0.5701563208157683</v>
+        <v>0.5821428571428572</v>
       </c>
     </row>
     <row r="593" spans="1:7">
@@ -26653,7 +26653,7 @@
         <v>0.4523809523809525</v>
       </c>
       <c r="G593">
-        <v>0.2604047674368849</v>
+        <v>0.2674603174603175</v>
       </c>
     </row>
     <row r="594" spans="1:7">
@@ -26676,7 +26676,7 @@
         <v>-0.09523809523809525</v>
       </c>
       <c r="G594">
-        <v>0.8225054302036112</v>
+        <v>0.8401289682539682</v>
       </c>
     </row>
     <row r="595" spans="1:7">
@@ -26699,7 +26699,7 @@
         <v>-0.04761904761904762</v>
       </c>
       <c r="G595">
-        <v>0.9108491685195835</v>
+        <v>0.9348710317460317</v>
       </c>
     </row>
     <row r="596" spans="1:7">
@@ -26722,7 +26722,7 @@
         <v>0.4761904761904763</v>
       </c>
       <c r="G596">
-        <v>0.2329355346500979</v>
+        <v>0.2430555555555556</v>
       </c>
     </row>
     <row r="597" spans="1:7">
@@ -26768,7 +26768,7 @@
         <v>0.1190476190476191</v>
       </c>
       <c r="G598">
-        <v>0.7788857260523797</v>
+        <v>0.7930059523809524</v>
       </c>
     </row>
     <row r="599" spans="1:7">
@@ -26791,7 +26791,7 @@
         <v>-0.4761904761904763</v>
       </c>
       <c r="G599">
-        <v>0.2329355346500979</v>
+        <v>0.2430555555555556</v>
       </c>
     </row>
     <row r="600" spans="1:7">
@@ -26814,7 +26814,7 @@
         <v>-0.642857142857143</v>
       </c>
       <c r="G600">
-        <v>0.08555889101267296</v>
+        <v>0.09618055555555556</v>
       </c>
     </row>
     <row r="601" spans="1:7">
@@ -26837,7 +26837,7 @@
         <v>0.2857142857142858</v>
       </c>
       <c r="G601">
-        <v>0.4927262450169571</v>
+        <v>0.5007936507936508</v>
       </c>
     </row>
     <row r="602" spans="1:7">
@@ -26860,7 +26860,7 @@
         <v>0.07142857142857144</v>
       </c>
       <c r="G602">
-        <v>0.8665262706759089</v>
+        <v>0.8819940476190476</v>
       </c>
     </row>
     <row r="603" spans="1:7">
@@ -26883,7 +26883,7 @@
         <v>-0.4047619047619048</v>
       </c>
       <c r="G603">
-        <v>0.3198886412288163</v>
+        <v>0.3268353174603175</v>
       </c>
     </row>
     <row r="604" spans="1:7">
@@ -26906,7 +26906,7 @@
         <v>-0.2857142857142858</v>
       </c>
       <c r="G604">
-        <v>0.4927262450169571</v>
+        <v>0.5007936507936508</v>
       </c>
     </row>
     <row r="605" spans="1:7">
@@ -26929,7 +26929,7 @@
         <v>-0.2380952380952381</v>
       </c>
       <c r="G605">
-        <v>0.5701563208157683</v>
+        <v>0.5821428571428572</v>
       </c>
     </row>
     <row r="606" spans="1:7">
@@ -26952,7 +26952,7 @@
         <v>-0.1666666666666667</v>
       </c>
       <c r="G606">
-        <v>0.693238811728395</v>
+        <v>0.7033234126984127</v>
       </c>
     </row>
     <row r="607" spans="1:7">
@@ -26975,7 +26975,7 @@
         <v>-0.1428571428571429</v>
       </c>
       <c r="G607">
-        <v>0.7357648598798121</v>
+        <v>0.7520337301587302</v>
       </c>
     </row>
     <row r="608" spans="1:7">
@@ -26998,7 +26998,7 @@
         <v>0.1428571428571429</v>
       </c>
       <c r="G608">
-        <v>0.7357648598798119</v>
+        <v>0.7520337301587302</v>
       </c>
     </row>
     <row r="609" spans="1:7">
@@ -27021,7 +27021,7 @@
         <v>-0.2619047619047619</v>
       </c>
       <c r="G609">
-        <v>0.5309228615658013</v>
+        <v>0.5364087301587301</v>
       </c>
     </row>
     <row r="610" spans="1:7">
@@ -27044,7 +27044,7 @@
         <v>-0.1190476190476191</v>
       </c>
       <c r="G610">
-        <v>0.7788857260523797</v>
+        <v>0.7930059523809524</v>
       </c>
     </row>
     <row r="611" spans="1:7">
@@ -27067,7 +27067,7 @@
         <v>0.2619047619047619</v>
       </c>
       <c r="G611">
-        <v>0.5309228615658013</v>
+        <v>0.5364087301587301</v>
       </c>
     </row>
     <row r="612" spans="1:7">
@@ -27090,7 +27090,7 @@
         <v>0.4523809523809525</v>
       </c>
       <c r="G612">
-        <v>0.2604047674368849</v>
+        <v>0.2674603174603175</v>
       </c>
     </row>
     <row r="613" spans="1:7">
@@ -27113,7 +27113,7 @@
         <v>-0.02380952380952381</v>
       </c>
       <c r="G613">
-        <v>0.9553740118158809</v>
+        <v>0.9767857142857143</v>
       </c>
     </row>
     <row r="614" spans="1:7">
@@ -27136,7 +27136,7 @@
         <v>0.4761904761904763</v>
       </c>
       <c r="G614">
-        <v>0.2329355346500979</v>
+        <v>0.2430555555555556</v>
       </c>
     </row>
     <row r="615" spans="1:7">
@@ -27159,7 +27159,7 @@
         <v>-0.2619047619047619</v>
       </c>
       <c r="G615">
-        <v>0.5309228615658013</v>
+        <v>0.5364087301587301</v>
       </c>
     </row>
     <row r="616" spans="1:7">
@@ -27182,7 +27182,7 @@
         <v>-0.3095238095238096</v>
       </c>
       <c r="G616">
-        <v>0.4556448907375821</v>
+        <v>0.4618055555555556</v>
       </c>
     </row>
     <row r="617" spans="1:7">
@@ -27205,7 +27205,7 @@
         <v>0.09523809523809525</v>
       </c>
       <c r="G617">
-        <v>0.8225054302036114</v>
+        <v>0.8401289682539682</v>
       </c>
     </row>
     <row r="618" spans="1:7">
@@ -27228,7 +27228,7 @@
         <v>-0.3095238095238096</v>
       </c>
       <c r="G618">
-        <v>0.4556448907375821</v>
+        <v>0.4618055555555556</v>
       </c>
     </row>
     <row r="619" spans="1:7">
@@ -27251,7 +27251,7 @@
         <v>0.09523809523809525</v>
       </c>
       <c r="G619">
-        <v>0.8225054302036114</v>
+        <v>0.8401289682539682</v>
       </c>
     </row>
     <row r="620" spans="1:7">
@@ -27274,7 +27274,7 @@
         <v>0.5714285714285715</v>
       </c>
       <c r="G620">
-        <v>0.1389599571607066</v>
+        <v>0.151140873015873</v>
       </c>
     </row>
     <row r="621" spans="1:7">
@@ -27297,7 +27297,7 @@
         <v>-0.5476190476190477</v>
       </c>
       <c r="G621">
-        <v>0.1600256425388963</v>
+        <v>0.1709821428571429</v>
       </c>
     </row>
     <row r="622" spans="1:7">
@@ -27320,7 +27320,7 @@
         <v>0.2142857142857143</v>
       </c>
       <c r="G622">
-        <v>0.6103444156452669</v>
+        <v>0.6190972222222222</v>
       </c>
     </row>
     <row r="623" spans="1:7">
@@ -27343,7 +27343,7 @@
         <v>-0.1666666666666667</v>
       </c>
       <c r="G623">
-        <v>0.693238811728395</v>
+        <v>0.7033234126984127</v>
       </c>
     </row>
     <row r="624" spans="1:7">
@@ -27366,7 +27366,7 @@
         <v>0.2857142857142858</v>
       </c>
       <c r="G624">
-        <v>0.4927262450169571</v>
+        <v>0.5007936507936508</v>
       </c>
     </row>
     <row r="625" spans="1:7">
@@ -27389,7 +27389,7 @@
         <v>-0.1190476190476191</v>
       </c>
       <c r="G625">
-        <v>0.7788857260523797</v>
+        <v>0.7930059523809524</v>
       </c>
     </row>
     <row r="626" spans="1:7">
@@ -27412,7 +27412,7 @@
         <v>0.5714285714285715</v>
       </c>
       <c r="G626">
-        <v>0.1389599571607066</v>
+        <v>0.151140873015873</v>
       </c>
     </row>
     <row r="627" spans="1:7">
@@ -27435,7 +27435,7 @@
         <v>-0.2619047619047619</v>
       </c>
       <c r="G627">
-        <v>0.5309228615658013</v>
+        <v>0.5364087301587301</v>
       </c>
     </row>
     <row r="628" spans="1:7">
@@ -27458,7 +27458,7 @@
         <v>-0.1904761904761905</v>
       </c>
       <c r="G628">
-        <v>0.6514014957024816</v>
+        <v>0.6645833333333333</v>
       </c>
     </row>
     <row r="629" spans="1:7">
@@ -27481,7 +27481,7 @@
         <v>0.1666666666666667</v>
       </c>
       <c r="G629">
-        <v>0.6932388117283947</v>
+        <v>0.7033234126984127</v>
       </c>
     </row>
     <row r="630" spans="1:7">
@@ -27504,7 +27504,7 @@
         <v>-0.2619047619047619</v>
       </c>
       <c r="G630">
-        <v>0.5309228615658013</v>
+        <v>0.5364087301587301</v>
       </c>
     </row>
     <row r="631" spans="1:7">
@@ -27527,7 +27527,7 @@
         <v>0.09523809523809525</v>
       </c>
       <c r="G631">
-        <v>0.8225054302036114</v>
+        <v>0.8401289682539682</v>
       </c>
     </row>
     <row r="632" spans="1:7">
@@ -27550,7 +27550,7 @@
         <v>0.6904761904761907</v>
       </c>
       <c r="G632">
-        <v>0.05799031816457269</v>
+        <v>0.06939484126984127</v>
       </c>
     </row>
     <row r="633" spans="1:7">
@@ -27573,7 +27573,7 @@
         <v>-0.5000000000000001</v>
       </c>
       <c r="G633">
-        <v>0.20703125</v>
+        <v>0.2161706349206349</v>
       </c>
     </row>
     <row r="634" spans="1:7">
@@ -27596,7 +27596,7 @@
         <v>0.380952380952381</v>
       </c>
       <c r="G634">
-        <v>0.3518125531175649</v>
+        <v>0.3598710317460317</v>
       </c>
     </row>
     <row r="635" spans="1:7">
@@ -27619,7 +27619,7 @@
         <v>-0.2380952380952381</v>
       </c>
       <c r="G635">
-        <v>0.5701563208157683</v>
+        <v>0.5821428571428572</v>
       </c>
     </row>
     <row r="636" spans="1:7">
@@ -27642,7 +27642,7 @@
         <v>0.1904761904761905</v>
       </c>
       <c r="G636">
-        <v>0.6514014957024816</v>
+        <v>0.6645833333333333</v>
       </c>
     </row>
     <row r="637" spans="1:7">
@@ -27665,7 +27665,7 @@
         <v>0.02380952380952381</v>
       </c>
       <c r="G637">
-        <v>0.9553740118158807</v>
+        <v>0.9767857142857143</v>
       </c>
     </row>
     <row r="638" spans="1:7">
@@ -27688,7 +27688,7 @@
         <v>0.4761904761904763</v>
       </c>
       <c r="G638">
-        <v>0.2329355346500979</v>
+        <v>0.2430555555555556</v>
       </c>
     </row>
     <row r="639" spans="1:7">
@@ -27711,7 +27711,7 @@
         <v>-0.2619047619047619</v>
       </c>
       <c r="G639">
-        <v>0.5309228615658013</v>
+        <v>0.5364087301587301</v>
       </c>
     </row>
     <row r="640" spans="1:7">
@@ -27734,7 +27734,7 @@
         <v>-0.3095238095238096</v>
       </c>
       <c r="G640">
-        <v>0.4556448907375821</v>
+        <v>0.4618055555555556</v>
       </c>
     </row>
     <row r="641" spans="1:7">
@@ -27757,7 +27757,7 @@
         <v>0.09523809523809525</v>
       </c>
       <c r="G641">
-        <v>0.8225054302036114</v>
+        <v>0.8401289682539682</v>
       </c>
     </row>
     <row r="642" spans="1:7">
@@ -27780,7 +27780,7 @@
         <v>-0.3095238095238096</v>
       </c>
       <c r="G642">
-        <v>0.4556448907375821</v>
+        <v>0.4618055555555556</v>
       </c>
     </row>
     <row r="643" spans="1:7">
@@ -27803,7 +27803,7 @@
         <v>0.09523809523809525</v>
       </c>
       <c r="G643">
-        <v>0.8225054302036114</v>
+        <v>0.8401289682539682</v>
       </c>
     </row>
     <row r="644" spans="1:7">
@@ -27826,7 +27826,7 @@
         <v>0.5714285714285715</v>
       </c>
       <c r="G644">
-        <v>0.1389599571607066</v>
+        <v>0.151140873015873</v>
       </c>
     </row>
     <row r="645" spans="1:7">
@@ -27849,7 +27849,7 @@
         <v>-0.5476190476190477</v>
       </c>
       <c r="G645">
-        <v>0.1600256425388963</v>
+        <v>0.1709821428571429</v>
       </c>
     </row>
     <row r="646" spans="1:7">
@@ -27872,7 +27872,7 @@
         <v>0.2142857142857143</v>
       </c>
       <c r="G646">
-        <v>0.6103444156452669</v>
+        <v>0.6190972222222222</v>
       </c>
     </row>
     <row r="647" spans="1:7">
@@ -27895,7 +27895,7 @@
         <v>-0.1666666666666667</v>
       </c>
       <c r="G647">
-        <v>0.693238811728395</v>
+        <v>0.7033234126984127</v>
       </c>
     </row>
     <row r="648" spans="1:7">
@@ -27918,7 +27918,7 @@
         <v>0.2857142857142858</v>
       </c>
       <c r="G648">
-        <v>0.4927262450169571</v>
+        <v>0.5007936507936508</v>
       </c>
     </row>
     <row r="649" spans="1:7">
@@ -27941,7 +27941,7 @@
         <v>-0.1190476190476191</v>
       </c>
       <c r="G649">
-        <v>0.7788857260523797</v>
+        <v>0.7930059523809524</v>
       </c>
     </row>
     <row r="650" spans="1:7">
@@ -27964,7 +27964,7 @@
         <v>-0.1666666666666667</v>
       </c>
       <c r="G650">
-        <v>0.693238811728395</v>
+        <v>0.7033234126984127</v>
       </c>
     </row>
     <row r="651" spans="1:7">
@@ -27987,7 +27987,7 @@
         <v>-0.6190476190476192</v>
       </c>
       <c r="G651">
-        <v>0.1017330374542645</v>
+        <v>0.1149801587301587</v>
       </c>
     </row>
     <row r="652" spans="1:7">
@@ -28010,7 +28010,7 @@
         <v>-0.2380952380952381</v>
       </c>
       <c r="G652">
-        <v>0.5701563208157683</v>
+        <v>0.5821428571428572</v>
       </c>
     </row>
     <row r="653" spans="1:7">
@@ -28033,7 +28033,7 @@
         <v>-0.6190476190476192</v>
       </c>
       <c r="G653">
-        <v>0.1017330374542645</v>
+        <v>0.1149801587301587</v>
       </c>
     </row>
     <row r="654" spans="1:7">
@@ -28056,7 +28056,7 @@
         <v>-0.1904761904761905</v>
       </c>
       <c r="G654">
-        <v>0.6514014957024816</v>
+        <v>0.6645833333333333</v>
       </c>
     </row>
     <row r="655" spans="1:7">
@@ -28079,7 +28079,7 @@
         <v>-0.7857142857142858</v>
       </c>
       <c r="G655">
-        <v>0.02081512725352529</v>
+        <v>0.0279265873015873</v>
       </c>
     </row>
     <row r="656" spans="1:7">
@@ -28102,7 +28102,7 @@
         <v>-0.1428571428571429</v>
       </c>
       <c r="G656">
-        <v>0.7357648598798121</v>
+        <v>0.7520337301587302</v>
       </c>
     </row>
     <row r="657" spans="1:7">
@@ -28125,7 +28125,7 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G657">
-        <v>0.4197530864197531</v>
+        <v>0.4278769841269841</v>
       </c>
     </row>
     <row r="658" spans="1:7">
@@ -28148,7 +28148,7 @@
         <v>-0.02380952380952381</v>
       </c>
       <c r="G658">
-        <v>0.9553740118158809</v>
+        <v>0.9767857142857143</v>
       </c>
     </row>
     <row r="659" spans="1:7">
@@ -28171,7 +28171,7 @@
         <v>-0.1666666666666667</v>
       </c>
       <c r="G659">
-        <v>0.693238811728395</v>
+        <v>0.7033234126984127</v>
       </c>
     </row>
     <row r="660" spans="1:7">
@@ -28194,7 +28194,7 @@
         <v>0.380952380952381</v>
       </c>
       <c r="G660">
-        <v>0.3518125531175649</v>
+        <v>0.3598710317460317</v>
       </c>
     </row>
     <row r="661" spans="1:7">
@@ -28217,7 +28217,7 @@
         <v>0.09523809523809525</v>
       </c>
       <c r="G661">
-        <v>0.8225054302036114</v>
+        <v>0.8401289682539682</v>
       </c>
     </row>
     <row r="662" spans="1:7">
@@ -28240,7 +28240,7 @@
         <v>-0.1666666666666667</v>
       </c>
       <c r="G662">
-        <v>0.693238811728395</v>
+        <v>0.7033234126984127</v>
       </c>
     </row>
     <row r="663" spans="1:7">
@@ -28263,7 +28263,7 @@
         <v>-0.5714285714285715</v>
       </c>
       <c r="G663">
-        <v>0.1389599571607063</v>
+        <v>0.151140873015873</v>
       </c>
     </row>
     <row r="664" spans="1:7">
@@ -28286,7 +28286,7 @@
         <v>-0.1904761904761905</v>
       </c>
       <c r="G664">
-        <v>0.6514014957024816</v>
+        <v>0.6645833333333333</v>
       </c>
     </row>
     <row r="665" spans="1:7">
@@ -28309,7 +28309,7 @@
         <v>-0.6666666666666667</v>
       </c>
       <c r="G665">
-        <v>0.07098765432098751</v>
+        <v>0.08308531746031746</v>
       </c>
     </row>
     <row r="666" spans="1:7">
@@ -28332,7 +28332,7 @@
         <v>-0.2142857142857143</v>
       </c>
       <c r="G666">
-        <v>0.6103444156452666</v>
+        <v>0.6190972222222222</v>
       </c>
     </row>
     <row r="667" spans="1:7">
@@ -28355,7 +28355,7 @@
         <v>-0.7380952380952382</v>
       </c>
       <c r="G667">
-        <v>0.03655276105286081</v>
+        <v>0.04583333333333333</v>
       </c>
     </row>
     <row r="668" spans="1:7">
@@ -28378,7 +28378,7 @@
         <v>-0.4285714285714287</v>
       </c>
       <c r="G668">
-        <v>0.2894032248467901</v>
+        <v>0.2992063492063492</v>
       </c>
     </row>
     <row r="669" spans="1:7">
@@ -28401,7 +28401,7 @@
         <v>0.1666666666666667</v>
       </c>
       <c r="G669">
-        <v>0.6932388117283947</v>
+        <v>0.7033234126984127</v>
       </c>
     </row>
     <row r="670" spans="1:7">
@@ -28424,7 +28424,7 @@
         <v>-0.02380952380952381</v>
       </c>
       <c r="G670">
-        <v>0.9553740118158809</v>
+        <v>0.9767857142857143</v>
       </c>
     </row>
     <row r="671" spans="1:7">
@@ -28447,7 +28447,7 @@
         <v>-0.1428571428571429</v>
       </c>
       <c r="G671">
-        <v>0.7357648598798121</v>
+        <v>0.7520337301587302</v>
       </c>
     </row>
     <row r="672" spans="1:7">
@@ -28470,7 +28470,7 @@
         <v>0.3571428571428572</v>
       </c>
       <c r="G672">
-        <v>0.3851206435562562</v>
+        <v>0.3893849206349206</v>
       </c>
     </row>
     <row r="673" spans="1:7">
@@ -28493,7 +28493,7 @@
         <v>0.1190476190476191</v>
       </c>
       <c r="G673">
-        <v>0.7788857260523797</v>
+        <v>0.7930059523809524</v>
       </c>
     </row>
     <row r="674" spans="1:7">
@@ -28516,7 +28516,7 @@
         <v>-0.4523809523809525</v>
       </c>
       <c r="G674">
-        <v>0.2604047674368849</v>
+        <v>0.2674603174603175</v>
       </c>
     </row>
     <row r="675" spans="1:7">
@@ -28539,7 +28539,7 @@
         <v>-0.3333333333333334</v>
       </c>
       <c r="G675">
-        <v>0.4197530864197531</v>
+        <v>0.4278769841269841</v>
       </c>
     </row>
     <row r="676" spans="1:7">
@@ -28562,7 +28562,7 @@
         <v>-0.09523809523809525</v>
       </c>
       <c r="G676">
-        <v>0.8225054302036112</v>
+        <v>0.8401289682539682</v>
       </c>
     </row>
     <row r="677" spans="1:7">
@@ -28585,7 +28585,7 @@
         <v>-0.6666666666666667</v>
       </c>
       <c r="G677">
-        <v>0.07098765432098751</v>
+        <v>0.08308531746031746</v>
       </c>
     </row>
     <row r="678" spans="1:7">
@@ -28608,7 +28608,7 @@
         <v>-0.02380952380952381</v>
       </c>
       <c r="G678">
-        <v>0.9553740118158809</v>
+        <v>0.9767857142857143</v>
       </c>
     </row>
     <row r="679" spans="1:7">
@@ -28631,7 +28631,7 @@
         <v>-0.5952380952380953</v>
       </c>
       <c r="G679">
-        <v>0.1195298061387926</v>
+        <v>0.1322916666666667</v>
       </c>
     </row>
     <row r="680" spans="1:7">
@@ -28654,7 +28654,7 @@
         <v>-0.7142857142857144</v>
       </c>
       <c r="G680">
-        <v>0.04652823228416715</v>
+        <v>0.05758928571428571</v>
       </c>
     </row>
     <row r="681" spans="1:7">
@@ -28677,7 +28677,7 @@
         <v>0.3571428571428572</v>
       </c>
       <c r="G681">
-        <v>0.3851206435562562</v>
+        <v>0.3893849206349206</v>
       </c>
     </row>
     <row r="682" spans="1:7">
@@ -28700,7 +28700,7 @@
         <v>-0.3095238095238096</v>
       </c>
       <c r="G682">
-        <v>0.4556448907375821</v>
+        <v>0.4618055555555556</v>
       </c>
     </row>
     <row r="683" spans="1:7">
@@ -28723,7 +28723,7 @@
         <v>0.1904761904761905</v>
       </c>
       <c r="G683">
-        <v>0.6514014957024816</v>
+        <v>0.6645833333333333</v>
       </c>
     </row>
     <row r="684" spans="1:7">
@@ -28746,7 +28746,7 @@
         <v>0.2619047619047619</v>
       </c>
       <c r="G684">
-        <v>0.5309228615658013</v>
+        <v>0.5364087301587301</v>
       </c>
     </row>
     <row r="685" spans="1:7">
@@ -28769,7 +28769,7 @@
         <v>0.1190476190476191</v>
       </c>
       <c r="G685">
-        <v>0.7788857260523797</v>
+        <v>0.7930059523809524</v>
       </c>
     </row>
     <row r="686" spans="1:7">
@@ -28792,7 +28792,7 @@
         <v>0.5030030300035688</v>
       </c>
       <c r="G686">
-        <v>0.2038766820084321</v>
+        <v>0.2089285714285714</v>
       </c>
     </row>
     <row r="687" spans="1:7">
@@ -28815,7 +28815,7 @@
         <v>-0.526955555241834</v>
       </c>
       <c r="G687">
-        <v>0.1796289671569267</v>
+        <v>0.1846230158730159</v>
       </c>
     </row>
     <row r="688" spans="1:7">
@@ -28838,7 +28838,7 @@
         <v>-0.2754540402400496</v>
       </c>
       <c r="G688">
-        <v>0.5090540726550731</v>
+        <v>0.5052579365079365</v>
       </c>
     </row>
     <row r="689" spans="1:7">
@@ -28861,7 +28861,7 @@
         <v>-0.3473116159548452</v>
       </c>
       <c r="G689">
-        <v>0.3992638742032817</v>
+        <v>0.3967261904761905</v>
       </c>
     </row>
     <row r="690" spans="1:7">
@@ -28884,7 +28884,7 @@
         <v>-0.3712641411931104</v>
       </c>
       <c r="G690">
-        <v>0.365202058019778</v>
+        <v>0.3626984126984127</v>
       </c>
     </row>
     <row r="691" spans="1:7">
@@ -28907,7 +28907,7 @@
         <v>-0.263477777620917</v>
       </c>
       <c r="G691">
-        <v>0.5283664705769091</v>
+        <v>0.5226190476190476</v>
       </c>
     </row>
     <row r="692" spans="1:7">
@@ -28930,7 +28930,7 @@
         <v>0.1796439392869889</v>
       </c>
       <c r="G692">
-        <v>0.670344277246939</v>
+        <v>0.6718253968253968</v>
       </c>
     </row>
     <row r="693" spans="1:7">
@@ -28953,7 +28953,7 @@
         <v>-0.5149792926227015</v>
       </c>
       <c r="G693">
-        <v>0.1915493134158658</v>
+        <v>0.197718253968254</v>
       </c>
     </row>
     <row r="694" spans="1:7">
@@ -28976,7 +28976,7 @@
         <v>0.2994065654783148</v>
       </c>
       <c r="G694">
-        <v>0.4712605287015583</v>
+        <v>0.4676587301587302</v>
       </c>
     </row>
     <row r="695" spans="1:7">
@@ -28999,7 +28999,7 @@
         <v>-0.1916202019061214</v>
       </c>
       <c r="G695">
-        <v>0.649410201122453</v>
+        <v>0.6466269841269842</v>
       </c>
     </row>
     <row r="696" spans="1:7">
@@ -29022,7 +29022,7 @@
         <v>0.3712641411931104</v>
       </c>
       <c r="G696">
-        <v>0.365202058019778</v>
+        <v>0.3626984126984127</v>
       </c>
     </row>
     <row r="697" spans="1:7">
@@ -29045,7 +29045,7 @@
         <v>0.2754540402400496</v>
       </c>
       <c r="G697">
-        <v>0.5090540726550731</v>
+        <v>0.5052579365079365</v>
       </c>
     </row>
     <row r="698" spans="1:7">
@@ -29068,7 +29068,7 @@
         <v>-0.6626987024788349</v>
       </c>
       <c r="G698">
-        <v>0.07330582330837648</v>
+        <v>0.08214285714285714</v>
       </c>
     </row>
     <row r="699" spans="1:7">
@@ -29091,7 +29091,7 @@
         <v>0.301226682944925</v>
       </c>
       <c r="G699">
-        <v>0.468435636896902</v>
+        <v>0.4619047619047619</v>
       </c>
     </row>
     <row r="700" spans="1:7">
@@ -29114,7 +29114,7 @@
         <v>0.289177615627128</v>
       </c>
       <c r="G700">
-        <v>0.4872612723244323</v>
+        <v>0.4845238095238095</v>
       </c>
     </row>
     <row r="701" spans="1:7">
@@ -29137,7 +29137,7 @@
         <v>0.204834144402549</v>
       </c>
       <c r="G701">
-        <v>0.6265435481779082</v>
+        <v>0.623015873015873</v>
       </c>
     </row>
     <row r="702" spans="1:7">
@@ -29160,7 +29160,7 @@
         <v>0.5060608273474739</v>
       </c>
       <c r="G702">
-        <v>0.2006906961272417</v>
+        <v>0.2055555555555555</v>
       </c>
     </row>
     <row r="703" spans="1:7">
@@ -29183,7 +29183,7 @@
         <v>0.228932279038143</v>
       </c>
       <c r="G703">
-        <v>0.5855140871254388</v>
+        <v>0.5845238095238096</v>
       </c>
     </row>
     <row r="704" spans="1:7">
@@ -29206,7 +29206,7 @@
         <v>-0.228932279038143</v>
       </c>
       <c r="G704">
-        <v>0.5855140871254392</v>
+        <v>0.5845238095238096</v>
       </c>
     </row>
     <row r="705" spans="1:7">
@@ -29229,7 +29229,7 @@
         <v>0.5060608273474739</v>
       </c>
       <c r="G705">
-        <v>0.2006906961272417</v>
+        <v>0.2055555555555555</v>
       </c>
     </row>
     <row r="706" spans="1:7">
@@ -29252,7 +29252,7 @@
         <v>-0.518109894665271</v>
       </c>
       <c r="G706">
-        <v>0.1883939303844395</v>
+        <v>0.1946428571428571</v>
       </c>
     </row>
     <row r="707" spans="1:7">
@@ -29275,7 +29275,7 @@
         <v>0.747042173703414</v>
       </c>
       <c r="G707">
-        <v>0.03317680393916268</v>
+        <v>0.04107142857142857</v>
       </c>
     </row>
     <row r="708" spans="1:7">
@@ -29298,7 +29298,7 @@
         <v>-0.108441605860173</v>
       </c>
       <c r="G708">
-        <v>0.7982604003862407</v>
+        <v>0.7972222222222223</v>
       </c>
     </row>
     <row r="709" spans="1:7">
@@ -29321,7 +29321,7 @@
         <v>-0.144588807813564</v>
       </c>
       <c r="G709">
-        <v>0.7326507408997528</v>
+        <v>0.7353174603174604</v>
       </c>
     </row>
     <row r="710" spans="1:7">
@@ -29344,7 +29344,7 @@
         <v>0.1428571428571429</v>
       </c>
       <c r="G710">
-        <v>0.7357648598798119</v>
+        <v>0.7520337301587302</v>
       </c>
     </row>
     <row r="711" spans="1:7">
@@ -29367,7 +29367,7 @@
         <v>0.07142857142857144</v>
       </c>
       <c r="G711">
-        <v>0.8665262706759089</v>
+        <v>0.8819940476190476</v>
       </c>
     </row>
     <row r="712" spans="1:7">
@@ -29390,7 +29390,7 @@
         <v>0.1428571428571429</v>
       </c>
       <c r="G712">
-        <v>0.7357648598798119</v>
+        <v>0.7520337301587302</v>
       </c>
     </row>
     <row r="713" spans="1:7">
@@ -29413,7 +29413,7 @@
         <v>0.09523809523809525</v>
       </c>
       <c r="G713">
-        <v>0.8225054302036114</v>
+        <v>0.8401289682539682</v>
       </c>
     </row>
     <row r="714" spans="1:7">
@@ -29436,7 +29436,7 @@
         <v>0.07142857142857144</v>
       </c>
       <c r="G714">
-        <v>0.8665262706759089</v>
+        <v>0.8819940476190476</v>
       </c>
     </row>
     <row r="715" spans="1:7">
@@ -29459,7 +29459,7 @@
         <v>0.2619047619047619</v>
       </c>
       <c r="G715">
-        <v>0.5309228615658013</v>
+        <v>0.5364087301587301</v>
       </c>
     </row>
     <row r="716" spans="1:7">
@@ -29482,7 +29482,7 @@
         <v>-0.04761904761904762</v>
       </c>
       <c r="G716">
-        <v>0.9108491685195835</v>
+        <v>0.9348710317460317</v>
       </c>
     </row>
     <row r="717" spans="1:7">
@@ -29505,7 +29505,7 @@
         <v>-0.2857142857142858</v>
       </c>
       <c r="G717">
-        <v>0.4927262450169571</v>
+        <v>0.5007936507936508</v>
       </c>
     </row>
     <row r="718" spans="1:7">
@@ -29528,7 +29528,7 @@
         <v>0.07142857142857144</v>
       </c>
       <c r="G718">
-        <v>0.8665262706759089</v>
+        <v>0.8819940476190476</v>
       </c>
     </row>
     <row r="719" spans="1:7">
@@ -29551,7 +29551,7 @@
         <v>0.2857142857142858</v>
       </c>
       <c r="G719">
-        <v>0.4927262450169571</v>
+        <v>0.5007936507936508</v>
       </c>
     </row>
     <row r="720" spans="1:7">
@@ -29574,7 +29574,7 @@
         <v>-0.02380952380952381</v>
       </c>
       <c r="G720">
-        <v>0.9553740118158809</v>
+        <v>0.9767857142857143</v>
       </c>
     </row>
     <row r="721" spans="1:7">
@@ -29597,7 +29597,7 @@
         <v>0.2142857142857143</v>
       </c>
       <c r="G721">
-        <v>0.6103444156452669</v>
+        <v>0.6190972222222222</v>
       </c>
     </row>
   </sheetData>
